--- a/data/google_news_dedup_17_0426_UTC_past2d.xlsx
+++ b/data/google_news_dedup_17_0426_UTC_past2d.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K77"/>
+  <dimension ref="A1:K82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,32 +480,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Brand Protest</t>
+          <t>BV Value Retail Crime</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>("Gucci" OR "Ralph Lauren" OR "Dior" OR "Armani" OR "Louis Vuitton" OR "Burberry" OR "Prada" OR "Nike" OR "Canada Goose" OR "Hugo Boss" OR "Moncler" OR "Saint Laurent" OR "Loro Piana" OR "Lacoste" OR "Versace" OR "Jimmy Choo" OR "Michael Kors" OR "Missoni" OR "Kiton" OR "Aquazzura" OR "Tumi") AND ("protest" OR "animal rights" OR "fur free" OR "PETA" OR "activist") AND -BAFTA AND -"red carpet" AND -"awards" AND -"wears" AND -"dressed in"</t>
+          <t>("Bicester Village") AND ("money laundering" OR "gang" OR "criminal" OR "fraud" OR "counterfeit")</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Before The Devil Wears Prada 2, Let's Rewatch These Films On The Fashion Industry - News18</t>
+          <t>Thames Valley Police boss urges for closure order extensions - Bicester Advertiser</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Before The Devil Wears Prada 2, Let's Rewatch These Films On The Fashion Industry - News18</t>
+          <t>Thames Valley Police boss urges for closure order extensions - Bicester Advertiser</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 08:48:03 GMT</t>
+          <t>Thu, 16 Apr 2026 15:05:18 GMT</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5gFBVV95cUxPN3dTSmpPNGdpVjBGY2E4c2VFSG1GLVY1aElmSTludTJrWEJuVFl5YlFDMnVkaEhZcU9hdW5FcmZyektNeEhTUnVpTnd1NjhvMWExWDh2U3ZOdElJYTRueXJTM09KUl9XTXFDTEwxdzgwX01mSHh5MmlyRE95bGk1UFVmZDhVbGpRVWs1Wk8yVEpXWGw0eEZOTTlsZF9fYXFvbmM3OUxuSEtfSlZ0T0tTb3pmZGVfZ21EM0NUWFdqNFBLbHNDTkRmal82VVlPNkJNVnZrcHdEQ2xxcGZyWHhBdmpTcDRad9IB6wFBVV95cUxNSl94bk1oaDFUU3JUWlRFdUlpOExnYldmRDV5RVlaTndDenVXRHNjMHBOYVpDTDdpRUhjMUF3WEdFbnJ2WFJnMUx4aW1KNkpMbWo2Z3R6SFZWY2NJMWtXRk9teE1YRzJYTzlCTndjbm5Ja0FSNTk2bllUR0JuYXJGU09nVlFFeHVxNkJxQ2lNTGFOOURYaC1aeXNuVEcyVlpDclJIbl94LU5RSHFpcG1sc0tlcWRzZW5xaV9OcWw0RVprM18ydGxBSDVZVVpBWVpTdmh6ZlFkaDRBR25LU0VlVnZsOVFpblIxNTNz?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPQTB2U1NONDMtT1FPVnRCUHkzQXlvbG1MbXBoV2RvOWNMbldXc0g4THQ2QkhmOXZyVTgwbmdQbDFjeml1V0hieXpTTnBjUWNqNS1EMzdPdldHSkI2Vk9NZTZqX20ycjJ5VW1pcWRacVZpRGd6eENEeE5QN2FEbEFWZWlvLU96NXlpS29OZGJHUDQ3LTFEQ0s5YlF4MGlXbXZYM0ZOR1p3?oc=5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -529,38 +529,38 @@
         </is>
       </c>
       <c r="K2" s="1" t="n">
-        <v>46128.36670138889</v>
+        <v>46128.62868055556</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BV Value Retail Crime (fallback)</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>("Bicester Village")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Four Seasons Hotel London at Park Lane to unveil new suites - Boutique Hotelier</t>
+          <t>Uber ups stake in Delivery Hero in £235 million deal - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Four Seasons Hotel London at Park Lane to unveil new suites - Boutique Hotelier</t>
+          <t>Uber ups stake in Delivery Hero in £235 million deal - Yahoo Finance UK</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 13:59:30 GMT</t>
+          <t>Fri, 17 Apr 2026 07:16:12 GMT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQclRxWnp0aDlycHJTSlZOTUxEcnBBR2FCa3dnSDhDUHVnOVhSMVpGMS1TVFlaM09CRGRzdXByVk1kanZLY1JfUUlWNkRTNEpqS05lUDJLQVdEV1doSFluQ0t1dngzZHdLdXhkOTJ1VGZ4ekdSRzV2Wkd5WFNJM1A1ZFZRQ2VybHVxRldOcDFCd1Y0TVlPT2xLTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxPU3NRaV9LX1dLRVBRdG5FNDJPNy1leU91RFQwTTVfRlRfdVp3SDVpM0dpQW1lZXN3eW9FeTVVR3RvLWdSdWlpYmpQeS1IX0h5bF9iMEpOMG0zaXVUM2pFVUh6WWxKYTFPSjZwY3JZSmM2enFBV0F6Q2wtblYwZlZsQXdfSQ?oc=5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -584,38 +584,38 @@
         </is>
       </c>
       <c r="K3" s="1" t="n">
-        <v>46128.58298611111</v>
+        <v>46129.30291666667</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BV Value Retail Crime (fallback)</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>("Bicester Village")</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Lebanese president refuses to speak to Israeli prime minister - Bicester Advertiser</t>
+          <t>DHL strike could disrupt JLR vehicle and parts supply - AM-online</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Lebanese president refuses to speak to Israeli prime minister - Bicester Advertiser</t>
+          <t>DHL strike could disrupt JLR vehicle and parts supply - AM-online</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 14:55:14 GMT</t>
+          <t>Fri, 17 Apr 2026 10:28:50 GMT</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitAFBVV95cUxQWGR2OV81b1NGajZTUVRGWTkxcS1LRmVwOVNPTHNRd0w2SWUxT1FORFZFcFFKRDc2MXBwUkRsNEhIMmVzMFRuOVdKYjItQVNFOWlyN21walR4T0ZSZm84YUxlemJXeWxjMG1lODlKNnZqUENaTFFKeWhjRFU1OTJoZVhvbWdrWkVRZUFtUXFhbFZBSnBOamliMFJPQlZMNmxELXJZVGpGSWdaZ3E1VnpET1g4aUc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijAFBVV95cUxOOHprdGhwcm5tTVk4QkxjVjFsakhZUUpueUFabkRnT0NfYnF1cGh3SnVRR2piT1FqdkdWQkFwNmR4VUJzdkFUb0NoTWVlajc3YVFQSjZTa25Ib2JhNHJsWE9LVkpRWm9KOWxPYmQ2MEZUR1NqV0ZkT3RZWTJmbHhMbGhsa0F6SmtvcXM0Wg?oc=5</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="K4" s="1" t="n">
-        <v>46128.62168981481</v>
+        <v>46129.43668981481</v>
       </c>
     </row>
     <row r="5">
@@ -655,22 +655,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Royal Mail and CWU reach agreement on USO reform - Parcel and Postal Technology International</t>
+          <t>A trick to get free delivery on Amazon | Money newsletter - revolutionradio.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Royal Mail and CWU reach agreement on USO reform - Parcel and Postal Technology International</t>
+          <t>A trick to get free delivery on Amazon | Money newsletter - revolutionradio.com</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 15:49:11 GMT</t>
+          <t>Thu, 16 Apr 2026 18:04:19 GMT</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQWndQMVpRcHZaN2lhNUhSQUpOX09ZUjBERDVCSEVRY3ZnaDJuQmcxYXVaTXdHZURJdHpOb18yNkw3emU5NThzZ19LY3NwUGdmQ1hzR0dvcTNZcFozc2o0dGVaWHR2RVFJQmpBSHJabFRtNy14ckgxaVFXS1YzNHRFeU5mekgtOTZXQndLMkVQMUhjeDZUYjA3TWFqaGUzY1NnNlVqRFZ5VXFKQlB0LVhYbGMxdmVLT3dSMkpXTlFfeE9FZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOYUc3TU80ZE5DNl9ZVWo3VHNYX19HT0E1d1hFNkEydTBLaXU3U2t6TmxRYzhsY25VcXdUNThUcVNqVWxyOEQzM3o4NzFCVGwyWjFjRHZHMFBfRlFaQnVpdkduU05qa2dieU9lQnRxTzlJaC1YYkNwSmdnZ2pOcWd1R2ZNc0tIYU1VNGozalZ4Y2NBVHdWNE5sNWZOM3djZGhQb3lnSg?oc=5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -694,7 +694,7 @@
         </is>
       </c>
       <c r="K5" s="1" t="n">
-        <v>46128.6591550926</v>
+        <v>46128.75299768519</v>
       </c>
     </row>
     <row r="6">
@@ -765,22 +765,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>A trick to get free delivery on Amazon | Money newsletter - revolutionradio.com</t>
+          <t>Riello VST 1100 1100VA UPS - Uninterruptible Power Supply With AVR, 98% Efficiency, For Computers &amp; Servers - ruhrkanal.news</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>A trick to get free delivery on Amazon | Money newsletter - revolutionradio.com</t>
+          <t>Riello VST 1100 1100VA UPS - Uninterruptible Power Supply With AVR, 98% Efficiency, For Computers &amp; Servers - ruhrkanal.news</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 18:04:19 GMT</t>
+          <t>Thu, 16 Apr 2026 20:35:10 GMT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxOYUc3TU80ZE5DNl9ZVWo3VHNYX19HT0E1d1hFNkEydTBLaXU3U2t6TmxRYzhsY25VcXdUNThUcVNqVWxyOEQzM3o4NzFCVGwyWjFjRHZHMFBfRlFaQnVpdkduU05qa2dieU9lQnRxTzlJaC1YYkNwSmdnZ2pOcWd1R2ZNc0tIYU1VNGozalZ4Y2NBVHdWNE5sNWZOM3djZGhQb3lnSg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxOVnZIZTBhNFgzZnpqcHk1Wnpfd3lTbzV4aU5UellDcGhDanVzdkdVV1FEbEllS0NPUUo2OC1TRnp5eFg1U0FOZ1ZxaXBmaGd1YkVRSzYydEtmN3ZmbVpKR19DUTBfMkMzS0hkd01oQjJFaHhYTFlOQ2x6NHZadEFZel9UYzJ6dUNJWG9id25yN00wQk42eHc?oc=5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46128.75299768519</v>
+        <v>46128.85775462963</v>
       </c>
     </row>
     <row r="8">
@@ -820,22 +820,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Video Shows Amazon Delivery Drone Dropping Package Directly Onto Concrete, Smashing Its Delicate Contents - Futurism</t>
+          <t>Florence Amazon driver in critical condition after brutal dog attack during delivery - WPDE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Video Shows Amazon Delivery Drone Dropping Package Directly Onto Concrete, Smashing Its Delicate Contents - Futurism</t>
+          <t>Florence Amazon driver in critical condition after brutal dog attack during delivery - WPDE</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 14:17:11 GMT</t>
+          <t>Fri, 17 Apr 2026 04:07:04 GMT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9ic2FRcW4tcy1NU1NmcHNjNTc3Rlh3UG9zcS16djl6em1Bd0oyMjZOZTBZR1dpLVBQQzRiVlRTYTY1YUZrdEF3Q1puRWNsd19YS1RISElOVnAzMWd4cUlaMWx1SDBZYTk0WHZpV05JQnFoTWsyTENZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAJBVV95cUxPN05nS0tqZ1RmQUo5Z3dhOGZkVDBUX3pQUmdHNFE1b3kxVGsySWpNZGd3T2Y2Wl9sNlFxMGQtNVFVQ2ZmNDk1RWRzWkJRN0ZTeGE1WGMybGNKM3lfbk9HQnZibWx3bEV0bjMyZTdRaXdRWjdqdTJ5SzIwTGhyUzJhWHdZZjNkd1laeWt6NjZ5Mk8tRks1XzFqUUIzZ2F4cXJsMmwwX1dTbm5MY2YtV3ZOeVVpLXFBNnUyU19PVnlLODhLb1NMa0hPWjA1X0s0Mko1cFVyT2hjbU5pUXBmaTVwNDRJWjdVLURPTHJrR0wtZ0Q0ZFdneWFvaDdwMUpVc2VUamlNUTJZZmVZYTRscGM2bmNRWm8zTWhaX0FBUQ?oc=5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -859,7 +859,7 @@
         </is>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46128.5952662037</v>
+        <v>46129.17157407408</v>
       </c>
     </row>
     <row r="9">
@@ -875,22 +875,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Florence Amazon driver in critical condition after brutal dog attack during delivery - WPDE</t>
+          <t>Video Shows Amazon Delivery Drone Dropping Package Directly Onto Concrete, Smashing Its Delicate Contents - Futurism</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Florence Amazon driver in critical condition after brutal dog attack during delivery - WPDE</t>
+          <t>Video Shows Amazon Delivery Drone Dropping Package Directly Onto Concrete, Smashing Its Delicate Contents - Futurism</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 04:07:04 GMT</t>
+          <t>Thu, 16 Apr 2026 14:17:11 GMT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAJBVV95cUxPN05nS0tqZ1RmQUo5Z3dhOGZkVDBUX3pQUmdHNFE1b3kxVGsySWpNZGd3T2Y2Wl9sNlFxMGQtNVFVQ2ZmNDk1RWRzWkJRN0ZTeGE1WGMybGNKM3lfbk9HQnZibWx3bEV0bjMyZTdRaXdRWjdqdTJ5SzIwTGhyUzJhWHdZZjNkd1laeWt6NjZ5Mk8tRks1XzFqUUIzZ2F4cXJsMmwwX1dTbm5MY2YtV3ZOeVVpLXFBNnUyU19PVnlLODhLb1NMa0hPWjA1X0s0Mko1cFVyT2hjbU5pUXBmaTVwNDRJWjdVLURPTHJrR0wtZ0Q0ZFdneWFvaDdwMUpVc2VUamlNUTJZZmVZYTRscGM2bmNRWm8zTWhaX0FBUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9ic2FRcW4tcy1NU1NmcHNjNTc3Rlh3UG9zcS16djl6em1Bd0oyMjZOZTBZR1dpLVBQQzRiVlRTYTY1YUZrdEF3Q1puRWNsd19YS1RISElOVnAzMWd4cUlaMWx1SDBZYTk0WHZpV05JQnFoTWsyTENZ?oc=5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="K9" s="1" t="n">
-        <v>46129.17157407408</v>
+        <v>46128.5952662037</v>
       </c>
     </row>
     <row r="10">
@@ -940,7 +940,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 01:45:53 GMT</t>
+          <t>Fri, 17 Apr 2026 08:44:28 GMT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46129.0735300926</v>
+        <v>46129.36421296297</v>
       </c>
     </row>
     <row r="11">
@@ -1040,22 +1040,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IOC ups auto LPG supply by 300% - The Times of India</t>
+          <t>Royal Mail delivery delays continue in Wales — 4 postcodes affected - MSN</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>IOC ups auto LPG supply by 300% - The Times of India</t>
+          <t>Royal Mail delivery delays continue in Wales — 4 postcodes affected - MSN</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 19:27:00 GMT</t>
+          <t>Fri, 17 Apr 2026 07:32:38 GMT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNeHhGbmt6VVFrOUNFMXFjOE5tWS1xZDBLT1dMbWxjVnVRMmw4SmlCSDNJT0prUFJMdHNYREpUZ2NIcDlhQlg4WFZydFBoUXRiOXlzMkNUbHRWWjJMY1lHRGhpRWlSV2p3MmpkaW1pRV9QSGdXU3JKLWxoYTVXYTJLMzE0RERVRkJEVjZDeWFyZmNqMGdQczk4UGZlYW94UUM5SWxPWGFqcE9vbU3SAbABQVVfeXFMTmhiOU83WF9qQ0lrN1JPeTFXX0wxbDlZbzQ3RmZSdFdDZFZSQ0MtWHlUV0QxOExvQTZNLURkbnVmd0lac3ZUS0d4R2pOT012N1VoWnM5bG1qMHpOY2IwMVdJZnhDWWlmYTVZU0RCdFY3QVhyd3NIaTdKdHRKQjNuaS01R0NabnBwcWV3OHRreGhCeFdxZFM2MkFILXlSaHZkQ1NVMThsSnBDcElSNzBKd3U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQVUw0NFBmc3c2VDBKWDd6bjRZbS1XcXpjenRFcC1YaFhETTY2cFlQTFRXeHZIendTd2hHN1pILWhNb3BuSVVMemc5dHh4eDM4TWozWmdvVDZPRFhEdTl6b2x3Z2ctZ2R1RDVTZmR4M2swSVRvNW9mOExxM1dSbUI0N3RoMHN0WkRBTU5HRW1HOU9ERk9uejZrbHRFRVJGSU5mZHB4Q05ORVpDSHdSZVc3Ylp3cWZQQQ?oc=5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1079,7 +1079,7 @@
         </is>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46128.81041666667</v>
+        <v>46129.3143287037</v>
       </c>
     </row>
     <row r="13">
@@ -1095,22 +1095,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Suspect Wanted After Accepting $25K FedEx Delivery Meant for Victim - The MoCo Show -</t>
+          <t>IOC ups auto LPG supply by 300% - The Times of India</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Suspect Wanted After Accepting $25K FedEx Delivery Meant for Victim - The MoCo Show -</t>
+          <t>IOC ups auto LPG supply by 300% - The Times of India</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 18:24:26 GMT</t>
+          <t>Thu, 16 Apr 2026 19:27:00 GMT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNcjVvdXlCSU5DOWRVWFlKQkJqM09jWGlzQ2VaX1FqcFJzdXQ1M1BpNVJYTnlhZW9rY2lxdVdsUzZOOGJSRWg3aGxvZUk4WnNVT1VUUzlFS3BicXAyNWxTUzE1bklDdTRXU282NnpTRnNYQmtmOU9FRjNGalV6ektaRVFYc0tXU2xoRUVWVzR5T3dFQkxTdklPOFAxdWdaQ21M?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqwFBVV95cUxNeHhGbmt6VVFrOUNFMXFjOE5tWS1xZDBLT1dMbWxjVnVRMmw4SmlCSDNJT0prUFJMdHNYREpUZ2NIcDlhQlg4WFZydFBoUXRiOXlzMkNUbHRWWjJMY1lHRGhpRWlSV2p3MmpkaW1pRV9QSGdXU3JKLWxoYTVXYTJLMzE0RERVRkJEVjZDeWFyZmNqMGdQczk4UGZlYW94UUM5SWxPWGFqcE9vbU3SAbABQVVfeXFMTmhiOU83WF9qQ0lrN1JPeTFXX0wxbDlZbzQ3RmZSdFdDZFZSQ0MtWHlUV0QxOExvQTZNLURkbnVmd0lac3ZUS0d4R2pOT012N1VoWnM5bG1qMHpOY2IwMVdJZnhDWWlmYTVZU0RCdFY3QVhyd3NIaTdKdHRKQjNuaS01R0NabnBwcWV3OHRreGhCeFdxZFM2MkFILXlSaHZkQ1NVMThsSnBDcElSNzBKd3U?oc=5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46128.76696759259</v>
+        <v>46128.81041666667</v>
       </c>
     </row>
     <row r="14">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Winn-Dixie delivery now available to Pensacola residents through Amazon - MSN</t>
+          <t>Suspect Wanted After Accepting $25K FedEx Delivery Meant for Victim - The MoCo Show -</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Winn-Dixie delivery now available to Pensacola residents through Amazon - MSN</t>
+          <t>Suspect Wanted After Accepting $25K FedEx Delivery Meant for Victim - The MoCo Show -</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 12:25:14 GMT</t>
+          <t>Thu, 16 Apr 2026 18:24:26 GMT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPUEo4c0xqVnJKamxJSEtFVXFEWTg3UlBoQTNyRElyMzQyR2xVaTdxLUNvdzNKWXMzZFY4QlVmdWF0ODlvb2JUWmpfWnZrOFJkeExkZDk1NG03WXp2SEJPei1HR2xRWkdLak5UMERRTThVRDFfRnB5TU1xcndqNHBuMFcwY1dWZUtadjg0bENzZzRPM1A0S2xpQVVmM0VLbXpVQjFpSm9QR08wMW5pZXVuYnlyYmNHSEZ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNcjVvdXlCSU5DOWRVWFlKQkJqM09jWGlzQ2VaX1FqcFJzdXQ1M1BpNVJYTnlhZW9rY2lxdVdsUzZOOGJSRWg3aGxvZUk4WnNVT1VUUzlFS3BicXAyNWxTUzE1bklDdTRXU282NnpTRnNYQmtmOU9FRjNGalV6ektaRVFYc0tXU2xoRUVWVzR5T3dFQkxTdklPOFAxdWdaQ21M?oc=5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1189,38 +1189,38 @@
         </is>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46128.51752314815</v>
+        <v>46128.76696759259</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BV Logistics Companies</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Who’s paying Amazon’s Canadian fuel surcharge, and how much is it? - CTV News</t>
+          <t>Slachtoffer schietpartij in Linnéstraat nog steeds kritiek - BRUZZ</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Who’s paying Amazon’s Canadian fuel surcharge, and how much is it? - CTV News</t>
+          <t>Shooting victim in Linnéstraat still critical - BRUZZ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 09:24:47 GMT</t>
+          <t>Fri, 17 Apr 2026 10:17:51 GMT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiuwFBVV95cUxQcU5icjBDaUJQazFFQzJQQ01VaTQwbHVuczVMTmtYUFVGS2VOQ1V6QllVMGZOaUFJRTNXdWZVU1BaR3dqdTR1bk9NLUhVa2JwREhyNlJmcVlJMDB3a0o1emU2NW94eTV0cWZHd2dja0JXWEdqVlJ5NzE5SE5yNTNuRXVHZTR1X0lhSFpTNWNRZGUtYVBVcjJ1TW1EX09GandERkQ4bUR5ZVRwcjlDanhLTEE3ZGNzUjRkczZv?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPdkdCN1FybldpblBwVVJJQXNMdHlvUXh1MHk3ZFVLM3QyOXRCYUpjdW5NU3JtZ05aeThtYzRJazJhOXQ2cVVlOXRPOElJaTRzdi14MGJCRnlBdXczb1E5MTEyakNET0lOVXcydTlZY0ZZUkQtcE5hdXN6QnUtN1FONmFldklaVUpYT19xaWJMNDJ5Mi1jSmVpUGUzeGxTSGU4XzNxRXc0SQ?oc=5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1230,21 +1230,21 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46128.39221064815</v>
+        <v>46129.4290625</v>
       </c>
     </row>
     <row r="16">
@@ -1260,22 +1260,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tiental wagens beschadigd na explosie in Sint-Gillis: al tweede incident op enkele dagen tijd - HBVL</t>
+          <t>Man die gewond raakte na schietpartij in Sint-Joost-ten-Node nog steeds in levensgevaar - Nieuwsblad</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Dozens of cars damaged after explosion in Sint-Gillis: second incident in a few days - HBVL</t>
+          <t>Man who was injured after shooting in Sint-Joost-ten-Noode still in danger of life - Nieuwsblad</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 19:50:56 GMT</t>
+          <t>Fri, 17 Apr 2026 11:41:06 GMT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOWTVfVUxzM0VYNW9iXzFnekJMbUsyY1JLRENCYXdObmFtTUNYZmJZZGtHbElCQUtCdTBTWGZLM0ZfZDRId1pkdFk1WHFrSXBTb0FYUWQ1WnNsMTZmRUd5aDdNSDNCOElIbXY2SmY4amU3UHBxdmtCeG9FSDdJT0NXT1pEVURUVzE0R1VyUnlqUjNscUdEUHgwT0EtSnpnbmptRUREeEd6NVVIQzlEajdzTVhnVUhiNGhDTUc0ZGcxU1B6ZjdxeWxzNE8tanQ2dkxfZG5pX19udnBaVVhuYlB5WVhR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxNbW5MMW11UGJUd0ZvbVFGZWI3WFNNRUlxYm5FVzlDUjFoRERRV2xEeExZME5CbjhscmNsNnVQV2pxWl9GZzNQLV9mY0F3bFpGcmhnTTBOUlZLamV6aDB4SUJiZU9HQ3Bhd2V6THJHR2g1dU9JV21OQlZ3RmVyejRselpjZjhDbUx6UGViT1JHM2RBeUh3QlNWSXMtWE9nOVBvb1V3WUdqSHQtbkQ0blZ1TmUwMmRZWHM5OWZnWm9FMXVOa1E2b2dweWx4YzVkMzVqa1BWeUdiNkVUYVZ0ZjFEVEI0UEs?oc=5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1299,7 +1299,7 @@
         </is>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46128.82703703704</v>
+        <v>46129.486875</v>
       </c>
     </row>
     <row r="17">
@@ -1315,22 +1315,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Explosie en beschietingen aan zelfde woning in Sint-Gillis: burgemeester vraagt hulp aan minister van Binnenlandse Zaken - VRT</t>
+          <t>Tiental wagens beschadigd na explosie in Sint-Gillis: al tweede incident op enkele dagen tijd - HBVL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Explosion and shelling at the same house in Sint-Gillis: mayor asks the Minister of the Interior for help - VRT</t>
+          <t>Dozens of cars damaged after explosion in Sint-Gillis: second incident in a few days - HBVL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 11:19:16 GMT</t>
+          <t>Thu, 16 Apr 2026 19:50:56 GMT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxOVHFSMVl6bmtwOEJ3WWtUOWwyTWEtdEhEbHRKd0UyY0pmX3V5VmpYdUY0Zld5b1h4a2lPdWV3RkdDVFNOaG9ab1RSYWJidm1WdE5mdVhvOXA4dEIyQUF5UVBfQTF6b0RqaXU2NjI1dW9RQ0ZvWktMbUpqQWYtZTVZenhLOUU2NFBfSmRCdzNEeEVlTU1rb0JTeUdCZndfWm5Ja2NWenlyb2U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4gFBVV95cUxOWTVfVUxzM0VYNW9iXzFnekJMbUsyY1JLRENCYXdObmFtTUNYZmJZZGtHbElCQUtCdTBTWGZLM0ZfZDRId1pkdFk1WHFrSXBTb0FYUWQ1WnNsMTZmRUd5aDdNSDNCOElIbXY2SmY4amU3UHBxdmtCeG9FSDdJT0NXT1pEVURUVzE0R1VyUnlqUjNscUdEUHgwT0EtSnpnbmptRUREeEd6NVVIQzlEajdzTVhnVUhiNGhDTUc0ZGcxU1B6ZjdxeWxzNE8tanQ2dkxfZG5pX19udnBaVVhuYlB5WVhR?oc=5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1354,7 +1354,7 @@
         </is>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46128.47171296296</v>
+        <v>46128.82703703704</v>
       </c>
     </row>
     <row r="18">
@@ -1370,22 +1370,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>“Moet ik misschien met een kogelvrij vest slapen?”: 83-jarige Fernande beleeft schrik van haar leven na zware explosie in Sint-Gillis - HLN</t>
+          <t>Explosie en beschietingen aan zelfde woning in Sint-Gillis: burgemeester vraagt hulp aan minister van Binnenlandse Zaken - MSN</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>“Should I perhaps sleep with a bulletproof vest?”: 83-year-old Fernande experiences the fright of her life after a major explosion in Sint-Gillis - HLN</t>
+          <t>Explosion and shelling at the same house in Sint-Gillis: mayor asks the Minister of the Interior for help - MSN</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 14:00:42 GMT</t>
+          <t>Fri, 17 Apr 2026 05:06:57 GMT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNQ3ljb3BaeC12OE9pbVNzSGZZa3c5dmpiWXF0d1E0UDRKMVB4NEF4QlhUSmNQNDlpaUVORjF0bHNxcTNxa012YlRianpQT1kzNGRsdl9GZUZqdzQ1T1JnT0p6TkJyem9DU1pxV1ljN21aRG1tcXVpN3YxVWU0U0NnR2dUZXVuamZvcVZleHQwZmt0YmJGTXdhdjZfdklBTnBDcW10ZXViREpMRnYwWlI1V2FFX0JZMDZTUExEV3pMRnRyVHlhOXowMElfVGxNbEROOUhwOE9sNm1fS0ZFdkp4Z2VxV2lNX3lzTXRGdmV4dURHclFqbEZ6cWx3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwAJBVV95cUxNalhVZEt1Z29QUE5pbGVENmtpYmFGTmYzeDVjOUlEcmNRQ0tGQnNXTUR0ZWFfOV9aSC1sczVlTERlU1dDNGhMUm1STWltY1BKNGJkODR6RnhBNkxRcnNnaHFOVUpMVmUwNFRYRnFWZkZsNW9RdV9TYTk5MENOYnl1R0JUTU1Hb1hHdWhPLXRmdWNoSW8tTEU3Wk1iTzRITGl2RnpZeHdjM05ibzg5a1JZRHJ0M3FyZGE2cmIxZ3ExZXgzdXRPZjZaRHpVdzJfVzhIOW5yQ0kyRWUzelNhWWFXdTl0S1FZQnZ5NjRFMWRHTjNmT3dqUE8tUjJybE5sWmpiZm81QmRVV3ZEUmRBNFkzSTB1OXJHS2UzMzYtU3I5eThlcExhWkJweHZycnpkZndGLWpGSjBBd2UtUHZzOTZZZA?oc=5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46128.58381944444</v>
+        <v>46129.21315972223</v>
       </c>
     </row>
     <row r="19">
@@ -1425,22 +1425,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Drugsgeweld houdt aan: opnieuw explosie in Sint-Gillis - v-nieuws</t>
+          <t>Persoon gewond na steekpartij in Koekelberg - BRUZZ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Drug violence continues: another explosion in Sint-Gillis - v-news</t>
+          <t>Person injured after stabbing in Koekelberg - BRUZZ</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 13:23:53 GMT</t>
+          <t>Fri, 17 Apr 2026 10:17:51 GMT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNUzloZEdic0hGYUdTcGJPbjd1bnJ0M3FJTmVxc29fOGRHdHJmNXR4RXIxeHRPT2FnSWltVTliOGRXcmtXSWhlSzFrSXN4N1JtXy0yRnRkRVFPUUl3aExlT2U3WWhjSFhkbENjUXMwUDRYZkJqdklURWFfMHM0WGoyRGNSWEY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxOZHlfelFWOHNBU244TmF4TXpRdVV2NlVXNkdpQzRkSFROM05HbHhSQzAwTDRSb19GSUZBNGxMbV9lRGtDRE5Bb282RURiV3l6ZHZ4cGxPSGxVV0k3U0JFeXFlQTh2R0xZMzI5Tnh3dDhhQzdBTDQtNlNrX0Z6ajBuVjVFYlRBV1k0dDJESDBQU3pZUVE?oc=5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46128.55825231481</v>
+        <v>46129.4290625</v>
       </c>
     </row>
     <row r="20">
@@ -1480,22 +1480,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brussel wil megabedrijven in Europa om te concurreren met China en VS: fuseren moet makkelijker worden - Brabants Dagblad</t>
+          <t>“Moet ik misschien met een kogelvrij vest slapen?”: 83-jarige Fernande beleeft schrik van haar leven na zware explosie in Sint-Gillis - HLN</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Brussels wants mega companies in Europe to compete with China and the US: merging must become easier - Brabants Dagblad</t>
+          <t>“Should I perhaps sleep with a bulletproof vest?”: 83-year-old Fernande experiences the fright of her life after a major explosion in Sint-Gillis - HLN</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 11:31:00 GMT</t>
+          <t>Thu, 16 Apr 2026 14:00:42 GMT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AFBVV95cUxPZ2FNbEFoVlRsUmpvb2ZwVUJvREJfMURIbENpdEFhR05LMkxPUHZrSFpPVTBOR1l3QlB0NWlSRTlmVVlPWnRkdUtLR1habDJLQi1oSjBmMTR0cVZicWhBRjEwNTIweS1QR2hrMHMxOXNpU0R1cUh5Z2NpVDBMYV9yTnE5eFRmQU8xZEN3TmcweTgxVG9ZeHZ5eXRMX1VxWEJFYkVxQlpjLWs0Z0JJOWFaaTR4Y3JQbFZkTkljRGlDLVNFVm10NmlKU3pfVUZkT0pNSTRydg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi-gFBVV95cUxNQ3ljb3BaeC12OE9pbVNzSGZZa3c5dmpiWXF0d1E0UDRKMVB4NEF4QlhUSmNQNDlpaUVORjF0bHNxcTNxa012YlRianpQT1kzNGRsdl9GZUZqdzQ1T1JnT0p6TkJyem9DU1pxV1ljN21aRG1tcXVpN3YxVWU0U0NnR2dUZXVuamZvcVZleHQwZmt0YmJGTXdhdjZfdklBTnBDcW10ZXViREpMRnYwWlI1V2FFX0JZMDZTUExEV3pMRnRyVHlhOXowMElfVGxNbEROOUhwOE9sNm1fS0ZFdkp4Z2VxV2lNX3lzTXRGdmV4dURHclFqbEZ6cWx3?oc=5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1519,7 +1519,7 @@
         </is>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46128.47986111111</v>
+        <v>46128.58381944444</v>
       </c>
     </row>
     <row r="21">
@@ -1535,22 +1535,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Reddingsactie na val van mergelwand vlak over de grens bij Maastricht - De Limburger</t>
+          <t>Drugsgeweld houdt aan: opnieuw explosie in Sint-Gillis - v-nieuws</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rescue operation after fall from marl wall just across the border near Maastricht - De Limburger</t>
+          <t>Drug violence continues: another explosion in Sint-Gillis - v-news</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 13:35:10 GMT</t>
+          <t>Thu, 16 Apr 2026 13:23:53 GMT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQZVd2UjlHZEM2UldiNDNROXc2Vk0xMmdqcHJESGNvdEJkUHVrSWdHdDhvR1Q3UHJ0OVRsa2RPVmNOWW5TZl9MSGxHZ1dHSmpRWnNCbS05RUJEdElteFg4SFFPZExGTmQydktxWEhULVVjdWJ3QUNEbFdLMzhOb3RzSGVlT0ROa0xObEtMR1N0bU96UGw5VHBjY04yMjM0OC1TLUlIU0dqUGdEbWhNSW5aZW9YYnMxNnlVSVRkNjNlV2lSUGVhV2dna0Fn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNUzloZEdic0hGYUdTcGJPbjd1bnJ0M3FJTmVxc29fOGRHdHJmNXR4RXIxeHRPT2FnSWltVTliOGRXcmtXSWhlSzFrSXN4N1JtXy0yRnRkRVFPUUl3aExlT2U3WWhjSFhkbENjUXMwUDRYZkJqdklURWFfMHM0WGoyRGNSWEY?oc=5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46128.56608796296</v>
+        <v>46128.55825231481</v>
       </c>
     </row>
     <row r="22">
@@ -1590,22 +1590,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Explosie in Sint-Gillis zorgt voor ravage - HLN</t>
+          <t>Reddingsactie na val van mergelwand vlak over de grens bij Maastricht - De Limburger</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Explosion in Sint-Gillis causes havoc - HLN</t>
+          <t>Rescue operation after fall from marl wall just across the border near Maastricht - De Limburger</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 10:00:26 GMT</t>
+          <t>Thu, 16 Apr 2026 13:35:10 GMT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxPZ0pWWVNrZm9FT3YtWFhUX1VuZEtWajEzQlN1Mlprb19nMHQzVHVkRlJxUXdaLTBXNUVoN0hVTThCX29tcG9VN0k2bE9qb3RYZTN5UW03ZnYzbk5JOHVvbzVHRVYzRDZXRXpHNzJ4YVlkcURXN1BtZjNKRGtrMTNVbWxvTDV2VmJERUJqTC1sRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxQZVd2UjlHZEM2UldiNDNROXc2Vk0xMmdqcHJESGNvdEJkUHVrSWdHdDhvR1Q3UHJ0OVRsa2RPVmNOWW5TZl9MSGxHZ1dHSmpRWnNCbS05RUJEdElteFg4SFFPZExGTmQydktxWEhULVVjdWJ3QUNEbFdLMzhOb3RzSGVlT0ROa0xObEtMR1N0bU96UGw5VHBjY04yMjM0OC1TLUlIU0dqUGdEbWhNSW5aZW9YYnMxNnlVSVRkNjNlV2lSUGVhV2dna0Fn?oc=5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1629,7 +1629,7 @@
         </is>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46128.4169675926</v>
+        <v>46128.56608796296</v>
       </c>
     </row>
     <row r="23">
@@ -1755,22 +1755,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Twee wagens 's nachts uitgebrand aan het Lemmensplein in Anderlecht - HLN</t>
+          <t>Frankrijk moet man die sinds onterechte en hardhandige arrestatie zwaar gehandicapt is 6,4 miljoen betalen - HLN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Two cars burned out at night at Lemmensplein in Anderlecht - HLN</t>
+          <t>France must pay 6.4 million to man who has been severely disabled since unjustified and harsh arrest - HLN</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 12:37:54 GMT</t>
+          <t>Fri, 17 Apr 2026 06:53:53 GMT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNNmR5QVhvMUFjZzVXeGl5MjN1Ny1RdF9pVGpWNElBNFdmb3VmeFZJVWpBNGNlWDMtY3BjbUJseHdNLVBJMWJ4djFhb1JOVzA4VFFUU0FZTjQ3bnRQMHQ5eFd6VXpqcGN3Q1hnUDVrUXUxM2M1dXA4QW9KaE9ua2xyZ3pOV0l2TDY0MmRHRGJaQS1SMU5NWGJVWm0xMGM4bUV5OXgyOFVR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgJBVV95cUxPS1M4QV9nV0Nld0dlNTdZcHJKc1FmaXZrS2NQblBuV0dwMWRLZE1aTHNzdkMyZHU0eERLNExqX2lmcUpGeEsxS2otd3ltaXd1TDQxSG5MclJzS1lCYzEwQThPaEJIUjBCZlVkekd0RkxHYnpycE5rbXhHcWg4OFZRQmdOUHByZkpjRGdoMzdQbW52N0RrX2wxdVJwbGZKZ1M1YUZnQ2JPSW85d3BTRkJTeFFWY2g4d2libFhNMlJwdXBSM3BmVEhjSmd1NUFjamlQN2hRV0xHdWJNMUVQSGVueU95d25aZ2VrZXlyTUc1S3B3Rm5ESFYxRy1vbkRBVEdoNzl4Nm9kclQyRFZqdGY1NzlFaHF5dHdYZVFsTmNSU1AyeVY3aHpUZEg0eUFMZw?oc=5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="K25" s="1" t="n">
-        <v>46128.52631944444</v>
+        <v>46129.28741898148</v>
       </c>
     </row>
     <row r="26">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Parket vraagt 4 jaar cel voor duo na aanslag in Plataanstraat: “We zijn die nacht niet eens in België geweest” - GVA</t>
+          <t>Veroordeelde drugscrimineel ‘Frank de Tank’ gearresteerd op Brussels Airport - HLN</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Public prosecutor asks for 4 years in prison for duo after attack in Plataanstraat: “We were not even in Belgium that night” - GVA</t>
+          <t>Convicted drug criminal 'Frank de Tank' arrested at Brussels Airport - HLN</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 13:46:00 GMT</t>
+          <t>Thu, 16 Apr 2026 16:47:17 GMT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxPRFZQNmJ1RGdxRTJWZUNUNHEwSFJENWpSY3hPdzA4bDlNZUJvLU5mbWpjeXpDTjQ2MG5vSkVpZDA2SUEtd1ZHX2NHbFFkdTc1VHhKSk4yNHE1TWo3ZzBucC00NzhRaVhKcGdkUXNlVFlZdGtJTWlSdXFHQ180Ql9oOFVtRzU3MG9ONV9TeUs0eE1qdUxuWHNIdEpnUHVmTHBseXcteDhpSVFkblNqa2FVUkpXVFBBUWJ0RmVOVEJWYkVYV3FmWmhUb1hrcHRLNW1HYmdmZlNIRlIzV21GaWhTbkZ0NnE2S082QVRhSm56SkRVampRNEpTSjEtRTB5RGhZLWZ4X0FraExrLXM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPN2xqUjVCWkN4U3JrV0d0UjJuV1lEQWhqcWFMTkJhX2lOaHNfTGlRX28ycDNkTS00blplUXJoWndDZ1dOWFR1a0tjd2U2cUJMdWxwWm16UUQ3Z2ZiRXlMODRlTjZEZ2NyVXZCWF9TT1l5bkJkbWp3YXJkanc0R2RoNkZlaHlEVE9YUllaenFYNUlIVkRobThWRERHbHFSQ3BfN3phV1VTVVpEalFqV1ZRTkd6MA?oc=5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46128.57361111111</v>
+        <v>46128.69950231481</v>
       </c>
     </row>
     <row r="27">
@@ -1865,22 +1865,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Veroordeelde drugscrimineel ‘Frank de Tank’ gearresteerd op Brussels Airport - pzc.nl</t>
+          <t>Parket vraagt 4 jaar cel voor duo na aanslag in Plataanstraat: “We zijn die nacht niet eens in België geweest” - GVA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Convicted drug criminal 'Frank de Tank' arrested at Brussels Airport - pzc.nl</t>
+          <t>Public prosecutor asks for 4 years in prison for duo after attack in Plataanstraat: “We were not even in Belgium that night” - GVA</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 09:17:00 GMT</t>
+          <t>Thu, 16 Apr 2026 13:46:00 GMT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPZGFYenpnenNJQ3IzQkxGaVRHUUVqZGYxcFB0d0poRldzaXFJR2xEMnoyYXNfYzJaQmNicmZ0MUxBb2EzU1poX0ZEcHpzZWlBNW5XWDdzeFRfcUE2Sk1sMUF4U3huUlQwbU1kNzQ0VmVjdjlqWS1KcGpSSjI3Uk9BbWU0X0c0MEZURVpIRlFqUjFqbTNwdU1KOHc2bzBSVzhzTDBZN29fMk9KOFcydF9tUHFTRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwJBVV95cUxPRFZQNmJ1RGdxRTJWZUNUNHEwSFJENWpSY3hPdzA4bDlNZUJvLU5mbWpjeXpDTjQ2MG5vSkVpZDA2SUEtd1ZHX2NHbFFkdTc1VHhKSk4yNHE1TWo3ZzBucC00NzhRaVhKcGdkUXNlVFlZdGtJTWlSdXFHQ180Ql9oOFVtRzU3MG9ONV9TeUs0eE1qdUxuWHNIdEpnUHVmTHBseXcteDhpSVFkblNqa2FVUkpXVFBBUWJ0RmVOVEJWYkVYV3FmWmhUb1hrcHRLNW1HYmdmZlNIRlIzV21GaWhTbkZ0NnE2S082QVRhSm56SkRVampRNEpTSjEtRTB5RGhZLWZ4X0FraExrLXM?oc=5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46128.38680555556</v>
+        <v>46128.57361111111</v>
       </c>
     </row>
     <row r="28">
@@ -1920,22 +1920,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Drugscrimineel Frank ‘De Tank’ gearresteerd op Zaventem na terugkeer uit Kenia - Nieuwsblad</t>
+          <t>Thomas Fazi: “De propagandamachine van Europa” – Hoe de EU ngo’s, media en universiteiten inzet voor propaganda - dagelijksestandaard.nl</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Drug criminal Frank 'De Tank' arrested at Zaventem after returning from Kenya - Nieuwsblad</t>
+          <t>Thomas Fazi: “Europe's propaganda machine” – How the EU uses NGOs, media and universities for propaganda - dagstandard.nl</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 10:05:36 GMT</t>
+          <t>Fri, 17 Apr 2026 12:00:53 GMT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8AFBVV95cUxNVDRtdlVfb21GVW5ndWppNFhSU1R1eFJ5cTVucUY2cWhzYUM3QlktY3BkbEJwTExOclppWl9BUzBubmR4OGRwT2tVcFBfYVMxbDZyN1R5aFFjWXhJTmxTVUxpOWFZTk41VUtXOUpidF9JN0R0ZXVndTJaV2VYNUc4eWJmZDRidkZfdnpRaFNLTjFWcUhvMEw0UEZkSTVVenp4TUxHTV9RT2lZOVV6LW91cEdsRmdfZWFoY2czb3VqM014NEJHU2FuY0tWWG95RE5yU0NDdU96c2xzdWdJQmJvaVBOTkRIbl8xYVI3VTg2cUo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxPWHh0cE1XLVR5WlFpbEpzSnJ0RC1Rdll2bFFBV3IySE1TVHhnaFlNZmJ5ZVRqczJxd19tTG40ZDVWR0JVcXZMdFphYWdXX0ljY1Btd2lXWXhaVEY5akxMX1NfY1J2aWU0TWNUMXF4Y2x3REhrWGtpdXd0dXZkQmRSajRGaF80RWRPaW1UdlowcXgwQjN5bHNVcUJ2eVdrZGJpWXpJZ29ueDRGdzBzUG9GdWZDTzlUMDVMdzlzT3dGcHNucG96dU9Uc1djaXR3eU1oWDN3c3RMa2lyZEs5T3ZmcVVSWUVuSWc?oc=5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1959,7 +1959,7 @@
         </is>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46128.42055555555</v>
+        <v>46129.50061342592</v>
       </c>
     </row>
     <row r="29">
@@ -1975,22 +1975,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Explosion damages 10 vehicles in Saint-Gilles - The Brussels Times</t>
+          <t>London police investigating possible terror attack near Israeli embassy - The Jerusalem Post</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Explosion damages 10 vehicles in Saint-Gilles - The Brussels Times</t>
+          <t>London police investigating possible terror attack near Israeli embassy - The Jerusalem Post</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 18:11:15 GMT</t>
+          <t>Fri, 17 Apr 2026 12:27:16 GMT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNc0Z5SkFfTkh4ZnM5LU9EN0FCSGxQSlZ0aXhJdnhzQUhUSTJHNlpTcGhMaUIteEpDODYtUkJmR1pOUXcxaE44ZDUxNmdIcFZPZF91VTR5SllYdWRLRnZuQXBxaHZoMy0yZFVKR2pQSl9zZ3VRY0FMaXJLMEdfamtaS3Vjd1g1NktnYmU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE94b0NGZXY0TjdyX1FJWnpYYTFldndRTkNETjBoUWhSYVVfaUViRERtV3lrZ0dQVnhwRWR6aEJHV2l4ZzhJNERSbWhkdENQZXE0Vi1mWGw4VVRvSnFLNWlJVjlvZ0FoZGRqdXc?oc=5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46128.7578125</v>
+        <v>46129.51893518519</v>
       </c>
     </row>
     <row r="30">
@@ -2030,22 +2030,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Antwerp stabbing: At least 6 injured after attack near pro-Kurdish demonstration in Belgium; suspects in custody - MSN</t>
+          <t>Europe’s Capital Shaken by Gang Wars and Explosions— Again - The European Conservative</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Antwerp stabbing: At least 6 injured after attack near pro-Kurdish demonstration in Belgium; suspects in custody - MSN</t>
+          <t>Europe’s Capital Shaken by Gang Wars and Explosions— Again - The European Conservative</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 03:31:47 GMT</t>
+          <t>Fri, 17 Apr 2026 11:04:26 GMT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgNBVV95cUxQbzJmb0tvbGVzQldjaFFCVFpJbGlEYWJ3MDBkWll3R0FoUGFkYVpqYWVZeW9QWTVGVHJHWEtPcGp6bUM2bExFcDRCV2lLazJxNmdvclhEZ3BLajh2MDFMNkR4cFhJZEUzdTRVN0JxbEowMXhFcGd0RXFEb1BfNV9aUEZlVHJfOGtNNHV0YjZwdlFwNVF6ZTh5cld0Q3JMOHV3UTZOZ3UyeUNtc1d5QXdjUTBwaHRxYjQ3LWlZYnE1Rzg5ckJFem8zLXo2djVXc0tHcTIybjRlaHhRNjctdlNMTDBsaUhTVW5uQ3VIUUpJNjMxUVdlblk5X2RTZkt5THFaeVRhekpGYzdGLTZuQkdVeTVRTWt0M24tVlFmUHFfY1hWZ3RxeVluNkl1RkFwVzc5ZXVOeGZWMDdlS3FlTHROZFFJTU4tZ1JLOUgzcUhRU2hVZUZYZGVsZ2dYOTlaWHNVMGdmem5JX1BpcTV0RlR5NVptVFBnQlZlX0N0NG5DYWtPeGZ6REE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxPVC03b2c3bWhyZDRxM283azROeHU5Wi1FdS1fY2NsOF9hX0pMbUFvZFdldHdTV3EzOVh5OE4wZDdGQXdiRVZjbkNQNzFGWmprRnhWdjMySFlERFBIbV8yVC1KU0JtRENITGdIOEdFWGs3SmN5N0U4R1lFNUROZ0lSYkF3YTB2WFpDZVIw?oc=5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46129.14707175926</v>
+        <v>46129.46141203704</v>
       </c>
     </row>
     <row r="31">
@@ -2085,22 +2085,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Explosion and gunfire at same Brussels property: mayor seeks help from Interior Minister - VRT</t>
+          <t>Explosion damages 10 vehicles in Saint-Gilles - The Brussels Times</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Explosion and gunfire at same Brussels property: mayor seeks help from Interior Minister - VRT</t>
+          <t>Explosion damages 10 vehicles in Saint-Gilles - The Brussels Times</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 12:21:26 GMT</t>
+          <t>Thu, 16 Apr 2026 22:26:39 GMT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxPOEtLWm9SUzdSWUZneG8xTFVLZzNKQlVnT1Faa1g0QnhUMkxNRklKSXpaM0RrUkRvemthcHp4SFcybU5GYmNiRzM1VlF3T3hLTnh6Rnk2LTYyRDFFQ0FCem45Vmg1dHdUeWNMU2JUUWl5cm9nQ2dWcmFCYUlYa01WbExpR3kxa2p4ck5ScXhMb3NxSDlQSHZMVHZEeG55ZjJTdTFneGhfRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiwFBVV95cUxNc0Z5SkFfTkh4ZnM5LU9EN0FCSGxQSlZ0aXhJdnhzQUhUSTJHNlpTcGhMaUIteEpDODYtUkJmR1pOUXcxaE44ZDUxNmdIcFZPZF91VTR5SllYdWRLRnZuQXBxaHZoMy0yZFVKR2pQSl9zZ3VRY0FMaXJLMEdfamtaS3Vjd1g1NktnYmU0?oc=5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="K31" s="1" t="n">
-        <v>46128.51488425926</v>
+        <v>46128.93517361111</v>
       </c>
     </row>
     <row r="32">
@@ -2140,22 +2140,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Fire destroys iconic Belgian singer's mural in Brussels - The Brussels Times</t>
+          <t>Antwerp stabbing: At least 6 injured after attack near pro-Kurdish demonstration in Belgium; suspects in custody - MSN</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Fire destroys iconic Belgian singer's mural in Brussels - The Brussels Times</t>
+          <t>Antwerp stabbing: At least 6 injured after attack near pro-Kurdish demonstration in Belgium; suspects in custody - MSN</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 16:15:43 GMT</t>
+          <t>Fri, 17 Apr 2026 03:31:47 GMT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxQb3QxZ09KakFUOFVreFVKZklNVGlUSVNzQTg2OWNKLWotZlBFNWJfWVFibFM1a2ZhTmJiZlFFQ015VFVneWw4bkc4YzdHaGNxTXFlaHdGZmxoaUxPbHliMkRDRkpGSVBVWlZwQ2dmc05zUnp4TWF3dE14WEZGVVBkeW9yRkVxZzkzMVRrdjhuS2FXRnYtamNZ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgNBVV95cUxQbzJmb0tvbGVzQldjaFFCVFpJbGlEYWJ3MDBkWll3R0FoUGFkYVpqYWVZeW9QWTVGVHJHWEtPcGp6bUM2bExFcDRCV2lLazJxNmdvclhEZ3BLajh2MDFMNkR4cFhJZEUzdTRVN0JxbEowMXhFcGd0RXFEb1BfNV9aUEZlVHJfOGtNNHV0YjZwdlFwNVF6ZTh5cld0Q3JMOHV3UTZOZ3UyeUNtc1d5QXdjUTBwaHRxYjQ3LWlZYnE1Rzg5ckJFem8zLXo2djVXc0tHcTIybjRlaHhRNjctdlNMTDBsaUhTVW5uQ3VIUUpJNjMxUVdlblk5X2RTZkt5THFaeVRhekpGYzdGLTZuQkdVeTVRTWt0M24tVlFmUHFfY1hWZ3RxeVluNkl1RkFwVzc5ZXVOeGZWMDdlS3FlTHROZFFJTU4tZ1JLOUgzcUhRU2hVZUZYZGVsZ2dYOTlaWHNVMGdmem5JX1BpcTV0RlR5NVptVFBnQlZlX0N0NG5DYWtPeGZ6REE?oc=5</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2179,7 +2179,7 @@
         </is>
       </c>
       <c r="K32" s="1" t="n">
-        <v>46128.67758101852</v>
+        <v>46129.14707175926</v>
       </c>
     </row>
     <row r="33">
@@ -2240,32 +2240,32 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Oil prices dip as market reacts calmly to Brussels attacks - ARY News</t>
+          <t>Explosion à Saint-Gilles: "C'est déjà le sixième incident dans cette maison. Nous ne pouvons plus tolérer cela" - BruxellesToday</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Oil prices dip as market reacts calmly to Brussels attacks - ARY News</t>
+          <t>Explosion in Saint-Gilles: “This is already the sixth incident in this house. We can no longer tolerate this” - BruxellesToday</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 13:56:20 GMT</t>
+          <t>Thu, 16 Apr 2026 15:01:00 GMT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxOczdUUGZBV0I0dEVjUHlUY0dpZ2M0LTFudUk2U250T0luWEFiNGowOFJrMWZmdUIxdlV0eXRCd2JQa3hUTmhOS3QtLWdCb3RPZ0gxTmEzckJOVlpicFpPclhqNGZGZGhrbGFqbllIVWxsSEVxR3BLOHN3ZE90N2NGNNIBgAFBVV95cUxOczdUUGZBV0I0dEVjUHlUY0dpZ2M0LTFudUk2U250T0luWEFiNGowOFJrMWZmdUIxdlV0eXRCd2JQa3hUTmhOS3QtLWdCb3RPZ0gxTmEzckJOVlpicFpPclhqNGZGZGhrbGFqbllIVWxsSEVxR3BLOHN3ZE90N2NGNA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPWFgyVGo0Nk9ybUh5YUxaY0ZUM3RwREM4cWtKbm95Y0ZxSWpoNDMyZTNiQ2F3Nk1XQTRYemNIU3pxVkNzRFdZTWpzbFRqOTROQWQxNUV0NnpLSmtYV1VMS0dxdDNIMjVNQXQ4VlBGTFRLeV9hOUFyM004SU1jUURWeUlPdkdHdF9iT01xRF9Jc0NXRzlWQWQzc1pFZDdtR2NiWE5HTGNR?oc=5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2285,11 +2285,11 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K34" s="1" t="n">
-        <v>46128.58078703703</v>
+        <v>46128.62569444445</v>
       </c>
     </row>
     <row r="35">
@@ -2305,22 +2305,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Explosion à Saint-Gilles: "C'est déjà le sixième incident dans cette maison. Nous ne pouvons plus tolérer cela" - BruxellesToday</t>
+          <t>Agression au couteau boulevard Anspach à Bruxelles - MSN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Explosion in Saint-Gilles: “This is already the sixth incident in this house. We can no longer tolerate this” - BruxellesToday</t>
+          <t>Knife attack on Boulevard Anspach in Brussels - MSN</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 15:01:00 GMT</t>
+          <t>Fri, 17 Apr 2026 04:35:06 GMT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPWFgyVGo0Nk9ybUh5YUxaY0ZUM3RwREM4cWtKbm95Y0ZxSWpoNDMyZTNiQ2F3Nk1XQTRYemNIU3pxVkNzRFdZTWpzbFRqOTROQWQxNUV0NnpLSmtYV1VMS0dxdDNIMjVNQXQ4VlBGTFRLeV9hOUFyM004SU1jUURWeUlPdkdHdF9iT01xRF9Jc0NXRzlWQWQzc1pFZDdtR2NiWE5HTGNR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAJBVV95cUxNbXlfeHFpclVYT1NCTkR3Zi1sSXR5d20taUt2SUREVThnQWV2LVBHLTR2NmwtQVhtQU5qYWJGMnR6S21mOVlRQTVSSGlVNkZreDhDbjlRSFdNUE13VGc5Q2NBSERGOFpVbUU1aFI5WEhSWWlEMF9LZlJqN290Ykp0ck45ZUtaaTNJc09sanRFUlNvMWV4dVBnM0hacnRla3FnTFJwTjVQWDdBTGdrSjhVVDllMUhkaUs1V3YxX0RReWhwNXNGU2pHVEdQVU9qQ01yMlY5dWxMck42Vng4blR3UXR5al8yRVZ3ek4xQ3NRX1d5MFJ5N0FMdV92WnJtcGhYWnFzMGJrc09sS3VZaUQzSUlweElQdW10Znk2Z2VNbEoydTRoTFFkd19jaF9kX2p5QU1aU2pMMmd2bWFybmF0QjJJWHQ?oc=5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="K35" s="1" t="n">
-        <v>46128.62569444445</v>
+        <v>46129.19104166667</v>
       </c>
     </row>
     <row r="36">
@@ -2360,22 +2360,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Saint-Gilles : la rue de Bosnie touchée par une explosion - BX1</t>
+          <t>Ukraine, attentat de la rue des Rosiers, ICE, Venezuela, Netflix : les informations de la nuit - Courrier international</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Saint-Gilles: rue de Bosnie hit by an explosion - BX1</t>
+          <t>Ukraine, attack on Rue des Rosiers, ICE, Venezuela, Netflix: the news of the night - Courrier international</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 11:14:00 GMT</t>
+          <t>Fri, 17 Apr 2026 03:00:03 GMT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOS3J0WXVQWTZYMVU3Zjg2VGk1X2N5bG5ydExjMEZwby1sSGV1UTFNcGVrcHdDQ19QTEJQdlFzT0ExU0ZoVXNaaGZlWVVEQ1FSZWg1WjZRU2FwTlBLX0VkbTZhQ0VrdU1KZmVVcFY3NElNRENxakVSMXkxazJNWkFNR0RHbmRyNm1qaHRVTlZSTFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOR3FGbGRuemlDSW5RZHdtVW9hQkxQQms0UzN5UnBqdlBWeGU4aVNvbDlNaUpvSHB0UENuRHpqTm9hQmtqcmN4V0JLQkpFRm9qYXVOdU5yRmxIcF9IRHRyc2RkZ1JlLVNOZzZBUmh0akp3RTY4TFlIMzFVMUo2dEhyRXB2NHFSc01aWW5rUlBjd3NFU2RuamxzN2VPQkVQd19rci1RQnhlSUdhYnZudkQ4MGtuUjNjVndZSUdxaGtRVEd0MVp3Zk0yaW0yZWRGSGdEWkZTQS1TUHViNnlUTlJ1eE5ISGNUbW5CaG5STFQ5Tks5RTY1?oc=5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46128.46805555555</v>
+        <v>46129.12503472222</v>
       </c>
     </row>
     <row r="37">
@@ -2415,22 +2415,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Une personne demandant l’aumône blessée à Bruxelles après une altercation - BX1</t>
+          <t>Migrants : Bruxelles appelle la Grèce à enquêter sur des refoulements présumés - Anadolu Ajansı</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>A person asking for alms injured in Brussels after an altercation - BX1</t>
+          <t>Migrants: Brussels calls on Greece to investigate alleged pushbacks - Anadolu Ajansı</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 13:04:00 GMT</t>
+          <t>Thu, 16 Apr 2026 15:02:50 GMT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQWUxrN2lqcGJpRUwzYjAwd2F5NkxnUlNYWVFzZWUzcklVX3l5c3NLZUVIU1RKRjNwSXpOX0dZcHNhVVNmOFJ0NTNhTG5yYlRxMWhhYXpiQm1MS2tKZzRkZEFuWXgwT2NJZHZZYTJmRzdGTHQ5QWhVX1N6bFlLV19DQkg5OFBZckVFSDBmTl9heGRtQmRLRk1qOVFhSmtQR01pNy1sRV9nTQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi1wFBVV95cUxPWFBsTEVPcFFrU2hfS1dVbC1Fc1FtZGpzUHZqOEVtY3ptME5GNUNHUTJBRGNGVVZBcmhVUGFmTWZvejl0SW9kNThnU0lvRWdIX0NxYmNkaUpZckJlSmozZHpyOWJpaXNsd3NzNTVhemoxbFdLMHlQRTVuUXR3MjAxeXZxS29VaERIbENkMHZ2bWo4VkZURV9ueWc2bUVDbFVNWE4tZGxsUjJhalpoOElmZXZWcW9iWFlLV1V2UzhJWjhoOFVSQ1Y3cDI5M205YXZHR2h0eW4tNA?oc=5</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46128.54444444444</v>
+        <v>46128.62696759259</v>
       </c>
     </row>
     <row r="38">
@@ -2470,22 +2470,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Patrick Bruel : “Juste bonne à ba*ser”, le mode opératoire “sale et glauque” du chanteur dénoncé par ces victimes présumées d’agression sexuelle - Marie France, magazine féminin</t>
+          <t>Patrick Bruel visé par une enquête en Belgique après la plainte d’une attachée de presse pour agression sexuelle - Gentside</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Patrick Bruel: “Just good to fuck”, the singer’s “dirty and murky” modus operandi denounced by these alleged victims of sexual assault - Marie France, women’s magazine</t>
+          <t>Patrick Bruel targeted by investigation in Belgium after press officer's complaint of sexual assault - Gentside</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 09:25:11 GMT</t>
+          <t>Thu, 16 Apr 2026 15:19:47 GMT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi-wFBVV95cUxNbmF1cFV0OFBJZ09laFNJdHlha0l4dVdnYmRHbGRGZC1pbVpQVFVieXZxRDF1MzAyUGxRbGxmVzhmZnBDaUxZUDlFRmw2TUdENkY0a2xJcW9yTUF3eUhYOUxoTnVpRTFtZVBHLURWd01kSTdndm11eUd6UkxRMXRtd20zYi1BRTZhT183ZWhJa0ZQT3lJWV9PbUZ2WHRjVC1iV3o1SkQ0cDdzQkdleHNYLWRNbE9vMDhqYUVQQnpTekFXVEpPNlJicUtoTUFPVWNrb1d6aUMyUk44QnFsbzh4SWY0RE4yQVl1OU83anhic1hvMGRFbEE3a1JtUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi7AFBVV95cUxOUlU2ZmdEUUV3TFNpYzBTT2VuMjAtMzQzakt0bUpMT2I2M0lPd2pBNEd0SHNpbkJJSHQ2RFhiSDhnSVBfM1FDVmh4ajlvUVZvd3ZIeGVSZ3ZXV0p0U3BLN1h2VG11ZlRQTFR4NGFYZkhsY3lKSkVYNklDYXBvU0tkTDNveVF1ejRxemhKZzhZa2lzT01Ta0g5S0dsVy02STY4T0o1T0tGekdhVERrZ0lETWt4SjNzUkQxTFZLVnlYa3RiMmV2YlFOdmtqZzFfdW1HcFYxTXF4UGFYSGU3X1VRSlVvX3RSUGc1dFZOaQ?oc=5</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2509,38 +2509,38 @@
         </is>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46128.39248842592</v>
+        <v>46128.63873842593</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen Dutch</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bom OR bommelding OR explosie OR schietpartij OR steekpartij OR evacuatie OR politie OR arrestatie) AND -sport AND -voetbal</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Explosief gegooid naar woning in Opgrimbie, dader vlucht weg op fatbike - VRT</t>
+          <t>Un banquet vide à Bruxelles pour dénoncer la précarité alimentaire - BX1</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Explosive thrown at home in Opgrimbie, perpetrator flees on fat bike - VRT</t>
+          <t>An empty banquet in Brussels to denounce food insecurity - BX1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 05:46:09 GMT</t>
+          <t>Thu, 16 Apr 2026 16:16:00 GMT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOeUVSMTdmNmNhSjVKekNLaHFQejlWNEtWN0M1bGIyZFFISnlObm1HU2NVc0VsdG9pcXJjcG1nMkRNN3RDQ2VrWVA1c2ZWLUlZMDJUekdIb3c4YUlQSGhHcEZPY0ZSTVBTRjBDS3drVDNJU1ExVXVBdU1DY09lbjZQamZ2YURmdGs?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxQcVZTQ0RuN3Bta0VvUE12aXhDOVlHQVM5NGRXdjBuNVBicFVlWEhDa3llYThKb1NNR0l4b0pwb3B6V2V2YkpyQlNEdVEyX3ViVHR3b28wV1Vwdi00MHVhR1dKNG1GZkMxUU5LTlBmOXN0amE4LUdLbUphWGR4OVkzR2Fwbk9KdUFQQnprd3N0cmhNaWM0dWU2aThPanBoaTZ2ZE54T0lrNA?oc=5</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2560,42 +2560,42 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46129.24038194444</v>
+        <v>46128.67777777778</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen Dutch</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bom OR bommelding OR explosie OR schietpartij OR steekpartij OR evacuatie OR politie OR arrestatie) AND -sport AND -voetbal</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Zeker een dode en verschillende gewonden bij schietpartij in Turkse basisschool - MSN</t>
+          <t>“Postcolonial?” : une nouvelle exposition sur l’héritage colonial européen à Bruxelles - BX1</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>At least one dead and several injured in shooting at Turkish primary school - MSN</t>
+          <t>“Postcolonial?” : a new exhibition on European colonial heritage in Brussels - BX1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 11:55:01 GMT</t>
+          <t>Thu, 16 Apr 2026 15:45:00 GMT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiygFBVV95cUxNV0VFWG1iTWNQRTlkaEpWdnhodGFfT09kTm1Ed0VmVU5GbVhWNF9QdGFpUmRpcFpPVzFxV0lVbUhlRmZNZjVRNWk0YmltZ0tSakdyREx5U2dXQTZhVHp0MVcteWpsY2ltaWpYX09IVC1BT3R1TUx0MTRqUUctUTNETU9DYVNzMnJabVVKNW9BeDlpVU1ic2ZkWXd0QkhWcWpQN19Hd0VJb2FvVTQ3UnNaaHR6dnVJTFBfS1p6TFdMbVhDM3FqYWp5Ty13?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxPSzdFMDZtbzVvU2NzcHZuejlFQ056MGR0WEJSSFQzMGZGeFNzOXpQdzBUWmZwdUFVZnZta1UwREs4Z1FZX1dQelNsazI4UldQSEJ3UkJ6dTJLTTVrUnNsbHJPUkM0TnA0SVkyWGVKSDRkTDFoczNuYTVYNlo3VGwzbzNFcU9JYzRrU2NyVmJaS1pnbjJuWnVNMHIzSHFOZDlBSHhIenFhNm1NZVFaTmlCSXVOb0c1Zw?oc=5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2615,42 +2615,42 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K40" s="1" t="n">
-        <v>46128.49653935185</v>
+        <v>46128.65625</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen Dutch</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bom OR bommelding OR explosie OR schietpartij OR steekpartij OR evacuatie OR politie OR arrestatie) AND -sport AND -voetbal</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Vrachtwagen met kraan botst tegen onderkant van spoorwegbrug in Hasselt: "Geen schade aan brug vastgesteld" - VRT</t>
+          <t>Des drones utilisés pour approvisionner plusieurs prisons belges en drogue: un réseau criminel démantelé - BruxellesToday</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Truck with crane collides with the underside of a railway bridge in Hasselt: "No damage to the bridge was found" - VRT</t>
+          <t>Drones used to supply several Belgian prisons with drugs: a criminal network dismantled - BruxellesToday</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 15:40:06 GMT</t>
+          <t>Thu, 16 Apr 2026 17:15:00 GMT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOdXV6TUppNVZlczJCanRJRnVKLTQwM1RZTFR0RTgyaHVXWklWUnVKNXRZaVZic0dGcW5ySTBMRW96Vl9rVVFfd2dSU0gwdG9iMFlyQ3hfNTA4Ung2bWpaWDZZU3Y0VTcxZG5iQlh2bFdzbUQzX1k5S3Q3T2k4QjdXckhoUmFFc0JRSFFjLVFaMTAzY1Y2?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxPTjd0YWd4RlRhZnhOZGxqSDlicFIxZHlPLXQ0Y1hfNS05RmNGUXhEeEhnbEZfVlIzVFoweWh6UDExUG1yRi1jc255N21yN1NmZ2ttQnNzclZ6MUoyWVI2ajNUc1FNR2tKTGp6LVl0d0NqNjc4Wkd5UWlDSVVBMi1zeG84UVJnd0JlQ2c?oc=5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2670,42 +2670,42 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K41" s="1" t="n">
-        <v>46128.65284722222</v>
+        <v>46128.71875</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen Dutch</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bom OR bommelding OR explosie OR schietpartij OR steekpartij OR evacuatie OR politie OR arrestatie) AND -sport AND -voetbal</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Explosie synagoge Luik - Militairen staan mee in voor beveiliging synagoge Luik - MSN</t>
+          <t>Affaire Patrick Bruel : TF1 diffuse des images déroutantes du chanteur aux côtés d’une des victimes présumées - Télé Star</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Synagogue explosion in Liège - Military personnel are responsible for the security of the synagogue in Liège - MSN</t>
+          <t>Patrick Bruel affair: TF1 broadcasts confusing images of the singer alongside one of the alleged victims - Télé Star</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 07:23:01 GMT</t>
+          <t>Thu, 16 Apr 2026 13:19:37 GMT</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4gJBVV95cUxOTi0taDBoZC1SRlc4Ny1icGxudjYwVjFoRW1RYVhIS0JFNTkxRldqM29kQlloUUxhWWdhakdtbGtMaEZhRjFVajdVSWJCVkN3dlc1Qlk0NDJoU3ZTRk9oUHdjTkpzamFhWkh2emU0eTh0ZmpsbVNPTlNldHRsdldsXzAyMmdEVUI0bzhNYVNGTWtHdVBhS0hGbThWYXpmcGR0SEkzMWdyQXppUTY0U2libUpIazZRTWw4NF9acGNpdktBdkdYZlpLS0hveFN6R0tqWk9PSnFMeFk2ODd1MzVZLW43eTdjbnRKbFF1aGdIQV9aV2NMbnc4a2ZJdG1WUnBDV2wyenZmOFIxSHhZc3REUWdhcWFBZDVMZnZXM25OV0RnR2gwS25PQjM4N2ZBLW4wclVsaVZJQnYwXy1yMlVBNUF3Uk1nOUc4MDczekNqMDB0TmtDajFQTmxNcWxmUnB5MWc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gFBVV95cUxOd01RRXM4TGVBUHdHN3dkWTBQUUFxYkt2QkdaOFp0X19WajJsQ2liWXdBVmNyNkVrNUo2cll5ZjlGamo5ZTlZZTNMTmVMeHhjeUxTNnVxcl9DOU9fVzdhUElVZzZsOERfWWZrYlRIQ2RDNjBHX1c1WlJKZlNqVXBVUXFRNkhJZFhxN3lsQ20tMkltQTBGRHREM2Z1Wi13ZkkyN19URGt5UGlTTGVxZTg2UVFXaHF6RmctbkhrN1BqSDZVOVM1ZDRwTjRDZzcwOU9nZ3ZYLXpsM25MUnQ4NHc?oc=5</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2725,42 +2725,42 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K42" s="1" t="n">
-        <v>46128.30765046296</v>
+        <v>46128.55528935185</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen French</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Une habitation de Maasmechelen visée par des explosifs - 7sur7.be</t>
+          <t>Attentat en 1982: le suspect palestinien Hicham Harb remis à la France - H24info</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>A house in Maasmechelen targeted by explosives - 7sur7.be</t>
+          <t>Attack in 1982: Palestinian suspect Hicham Harb handed over to France - H24info</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 06:30:49 GMT</t>
+          <t>Fri, 17 Apr 2026 08:29:45 GMT</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOY3p4c05CMktsYVFIN21xLVFwdENDTGk3S3ViM2RFVXNESWJzUHlaVEJTMHU0eHRLQ2lRT2loVXVtUkxSSUdTZmdKbndYcDhFbGJCOVQ1cUVBMGMtQnRFM3VHbENsQ2tRMzZaSHNLT2dqdjMxdVZYXzUzajJwZmpwMzJjWW5rWWJ6NkZWNU1mQTlhem9nZlZaWFJ3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivgFBVV95cUxPQzAwb2VuTVl0OVRpbnpuSDcyUEU3UXoxeHRBaU5hZV95amFqUkxuMUN0X3B1LVZqTmxvLW9IRGhWSlNyQ3FvVzVKWjJxWWJDT2dBcGFfWU9HMHNnU0oteXBQQU5mVm5jRHNCd1gwNlhvbWpNdlh4ekQ0YlN3ZHNpT3ozeFBXQ2F2ZnJYTWQ1X2x3Z2t3VThlcTgwQTM1THM0Q3VBMUdpbWZCUUEwOUJ4ZlNJb1NERFdBc0dXMVp3?oc=5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2784,38 +2784,38 @@
         </is>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46129.27140046296</v>
+        <v>46129.35399305556</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen French</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Une avocate belge donne naissance à l’enfant d’un meurtrier condamné à la prison à perpétuité - 7sur7.be</t>
+          <t>« C’est un chasseur et nous sommes des proies » : une plaignante de Patrick Bruel témoigne au JT de TF1 - MSN</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Belgian lawyer gives birth to child of murderer sentenced to life in prison - 7sur7.be</t>
+          <t>“He is a hunter and we are prey”: a complainant of Patrick Bruel testifies to the TF1 news - MSN</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 07:08:00 GMT</t>
+          <t>Fri, 17 Apr 2026 11:11:33 GMT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0AFBVV95cUxNMXIwcHF4MXN1MEtJLWlKUTdjZVVYMDBIUmlLZUdmSXVkQS1NbU9Tc3BTZEdvT3hyQnpKZjQ2STAyYzJ0WHBMZmcxRXl5XzJ6YTdPODVZM0YxX2FLQWhpUUthME9HUy1EbXZRYkQ1RVktYjRyRE5MS3Yydnc2dlAtbzJ4R3BjWWZVNlNEbWctYWppM2tqczRMU3dVOEstcHUtek4xTUQybnZ5VFl4Z2NOOVhZcFFaZXhRQVRQWTZLMkQ3MXpCemp5OGM5ZVRJN3pS?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihANBVV95cUxNTDdISGNoUktOdHhITWg5MXpVVGNxTm1IUjRJMWtmdDhRUEZZcnpiOF9JZmhQZjNrRGJra0pWTFZ2dGJVMHktUGoySzJXMmZFbE5rZjJrNmVJSlFQekNiT1VCdHMxS1FBWk1jM1J6WFJ0R2xWS0NIMnpJMHRUS2cta3k2UkUwcWRpdnR6RVQyaE5OaGNGMXVuOTJITUMtNUZjdHBHd1ZtN3ExOEd4OFluQXNESzdjZGZWZkRyd1VGamk0X0pyUWhuN1VHUXVobFU3TjNuYUJMTzNRV21FNElYU3hNUFRQMFlRWk1LNDdsTlhORXloWmdFRHRseTNRbHV3MjJ6dGhpbW5IYzJMaW5KVUIzRTBlLWR3N1ZGdlVtcTBxWjh5cEhLUFM5bzE3LVJfU1Q2cUNWQTdNZDE3OE5Zd1JFMlhMdFdYV0ZJaHZmbkYwVHVnNHJuOUppYXdJNzBwaHc2XzNKRmlnZlVWS1B1NnA4MVJsT19KTEtnYzRBV3ZaaS0x?oc=5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2839,38 +2839,38 @@
         </is>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46128.29722222222</v>
+        <v>46129.46635416667</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen French</t>
+          <t>Local Town Maasmechelen Dutch</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bom OR bommelding OR explosie OR schietpartij OR steekpartij OR evacuatie OR politie OR arrestatie) AND -sport AND -voetbal</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Une habitation de Maasmechelen visée par des explosifs - DHnet</t>
+          <t>Vuurwerkbom ontploft aan woning in Opgrimbie, dader vlucht weg op fatbike - VRT</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>A house in Maasmechelen targeted by explosives - DHnet</t>
+          <t>Fireworks bomb explodes at home in Opgrimbie, perpetrator flees on fat bike - VRT</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 06:34:00 GMT</t>
+          <t>Fri, 17 Apr 2026 05:46:09 GMT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOX084QVdTN3Z0MGQybndoVS1sZEprUTVUQ1VzcGY0amVkUGJzWTlBMGE0b3czRGNQWWxNQ01sMVpRaWhrT2p4SzZ6SWxBeEhnOTU0U0Z6Z19XdFBzWGV3ZktGS0lOQUYyU2liM3RQczBVZlVKbWRFVmxOczgyWENHV0djcjd4ZklLMWlSbmNaYUtaa2VWVG1zc1p4S2loYzJDN3JlSXI0eFQ2TzhSQWRKMzFJaXZUY1F3TkRFeUdRTHctYUtiN2dyUm82eVJMdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxOeUVSMTdmNmNhSjVKekNLaHFQejlWNEtWN0M1bGIyZFFISnlObm1HU2NVc0VsdG9pcXJjcG1nMkRNN3RDQ2VrWVA1c2ZWLUlZMDJUekdIb3c4YUlQSGhHcEZPY0ZSTVBTRjBDS3drVDNJU1ExVXVBdU1DY09lbjZQamZ2YURmdGs?oc=5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2890,42 +2890,42 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46129.27361111111</v>
+        <v>46129.24038194444</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen English (fallback)</t>
+          <t>Local Town Maasmechelen Dutch</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (protest OR bom OR bommelding OR explosie OR schietpartij OR steekpartij OR evacuatie OR politie OR arrestatie) AND -sport AND -voetbal</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Monaco interested in PSG prospect - Get French Football News</t>
+          <t>Vrachtwagen met kraan botst tegen onderkant van spoorwegbrug in Hasselt: "Geen schade aan brug vastgesteld" - VRT</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Monaco interested in PSG prospect - Get French Football News</t>
+          <t>Truck with crane collides with the underside of a railway bridge in Hasselt: "No damage to the bridge was found" - VRT</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 09:48:45 GMT</t>
+          <t>Thu, 16 Apr 2026 15:40:06 GMT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigwFBVV95cUxOVWFvbTh1dmRGMjFyZ1kwbnZKNzQxYVpLdnVRODYzWkoyOVBCTXBxRmZzYnBkaU1NU0VHbkp3UnhJb1o4czhkTTdnSVNaS1laQWpGVVdNbDU5eVFRM2tBVEh2aUl0WnlKM3Znd1VLU2ZlMmxzdGhlMWRqbUtIVmJSVDVlUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOdXV6TUppNVZlczJCanRJRnVKLTQwM1RZTFR0RTgyaHVXWklWUnVKNXRZaVZic0dGcW5ySTBMRW96Vl9rVVFfd2dSU0gwdG9iMFlyQ3hfNTA4Ung2bWpaWDZZU3Y0VTcxZG5iQlh2bFdzbUQzX1k5S3Q3T2k4QjdXckhoUmFFc0JRSFFjLVFaMTAzY1Y2?oc=5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2935,52 +2935,52 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K46" s="1" t="n">
-        <v>46128.40885416666</v>
+        <v>46128.65284722222</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen English (fallback)</t>
+          <t>Local Town Maasmechelen French</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Jewellery beyond the personal - A conversation with Maria Konschake about the relation between jewellery, memory, and identity - Metropolis M</t>
+          <t>Une habitation de Maasmechelen visée par des explosifs - DHnet</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Jewellery beyond the personal - A conversation with Maria Konschake about the relation between jewellery, memory, and identity - Metropolis M</t>
+          <t>A house in Maasmechelen targeted by explosives - DHnet</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 09:27:34 GMT</t>
+          <t>Fri, 17 Apr 2026 06:34:00 GMT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQQkJMX0RsaThhWEtObmJfbU9kdm1yWE9VYlB4NjFrakFSZldiLUZJY1NzLXBtcnFNMlJwMTlGRlgwQVVkemItU1RXMG45Zzlud25oQzc1eXc3RVQzejQxRWlQSW5Xa3pCZWxCSHIxek4zVy1DdzBULUNESEtzdUVtQ1E2cjBIVU9penZUWllXN1hCQVMxQkN0cnZXbGktMWd0M1Jn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMizgFBVV95cUxOX084QVdTN3Z0MGQybndoVS1sZEprUTVUQ1VzcGY0amVkUGJzWTlBMGE0b3czRGNQWWxNQ01sMVpRaWhrT2p4SzZ6SWxBeEhnOTU0U0Z6Z19XdFBzWGV3ZktGS0lOQUYyU2liM3RQczBVZlVKbWRFVmxOczgyWENHV0djcjd4ZklLMWlSbmNaYUtaa2VWVG1zc1p4S2loYzJDN3JlSXI0eFQ2TzhSQWRKMzFJaXZUY1F3TkRFeUdRTHctYUtiN2dyUm82eVJMdw?oc=5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2990,52 +2990,52 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K47" s="1" t="n">
-        <v>46128.39414351852</v>
+        <v>46129.27361111111</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen English (fallback)</t>
+          <t>Local Town Maasmechelen French</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kipyegon to open season in Keqiao 5000m - Citizen Digital</t>
+          <t>Une habitation de Maasmechelen visée par des explosifs - 7sur7.be</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Kipyegon to open season in Keqiao 5000m - Citizen Digital</t>
+          <t>A house in Maasmechelen targeted by explosives - 7sur7.be</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 12:24:58 GMT</t>
+          <t>Fri, 17 Apr 2026 06:30:49 GMT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipwFBVV95cUxNV2x5dDEweUZSaEpXSzN0RUFIZHZBVVRzYlVzSmhQMUVxNUZfbm8xVzFRVGNqZW00bm1BVGFfei1LSU1LSDZ5OEdBTFpJRWNqQUNpVldUelVRWnJXdkU5M3F2aWJsRDQzeDhITXZ4bFNXeERTalNqUWpYeXhSY3M4UE00b0cxS0MtV2h0V2VBQUp5cGhvSTB4WHdGemxicE5WQXZOOVpvaw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimgFBVV95cUxOY3p4c05CMktsYVFIN21xLVFwdENDTGk3S3ViM2RFVXNESWJzUHlaVEJTMHU0eHRLQ2lRT2loVXVtUkxSSUdTZmdKbndYcDhFbGJCOVQ1cUVBMGMtQnRFM3VHbENsQ2tRMzZaSHNLT2dqdjMxdVZYXzUzajJwZmpwMzJjWW5rWWJ6NkZWNU1mQTlhem9nZlZaWFJ3?oc=5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3045,52 +3045,52 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K48" s="1" t="n">
-        <v>46128.51733796296</v>
+        <v>46129.27140046296</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>High Level City Germany English</t>
+          <t>Local Town Maasmechelen French</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("Frankfurt" OR "Cologne" OR "Munich" OR "Stuttgart" OR "Germany") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror attack" OR protest OR strike OR riot OR "hate crime" OR "antisemitic" OR "vandalism" OR "attack") AND -football AND -soccer AND -Bundesliga AND -Bayern</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lufthansa strike cancels hundreds of flights across Germany - Anadolu Ajansı</t>
+          <t>Les défis d'emploi pour les diabétiques en France : un constat amer après la loi de 2021 - actuistres.fr</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Lufthansa strike cancels hundreds of flights across Germany - Anadolu Ajansı</t>
+          <t>Employment challenges for diabetics in France: a bitter observation after the 2021 law - actuistres.fr</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 08:02:47 GMT</t>
+          <t>Fri, 17 Apr 2026 11:12:35 GMT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiogFBVV95cUxPNkNUdDgwV1lTeFNTTkJBbmFzSDkwS3pXVmJ4OHhNUWlmSHk3bHdDVjNFQmdQb0FtMmlZVnFWTTZVWVFIdTgzbzd1dWxoMHhxZlNOWnZKNEdVV29iN0drenpzV3lPRUc1WkhSbTRUUk4zaEp5Tll6S19UaElWcXV4SUZRVWZZZFNoRTExck1GLUJVOWxvdzdkYnNnWl93R2lfZlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUEFVX3lxTFBqSTJwRkhJeUltNnk2QVFkU2pyVHFJcnNKQzA2b2pDcDBIcEZ4cVAyejQ4dVFhM2c2UndhUGVMUTNjMjdReVV6QUxxR1J2RlE5?oc=5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3100,52 +3100,52 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>DE:en</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K49" s="1" t="n">
-        <v>46128.33526620371</v>
+        <v>46129.46707175926</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Village Wertheim (fallback)</t>
+          <t>High Level City Germany English</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Frankfurt" OR "Cologne" OR "Munich" OR "Stuttgart" OR "Germany") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror attack" OR protest OR strike OR riot OR "hate crime" OR "antisemitic" OR "vandalism" OR "attack") AND -football AND -soccer AND -Bundesliga AND -Bayern</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Copter Rescues Teen Stuck In Mud At Wertheim National Refuge - MSN</t>
+          <t>Lufthansa pilots’ strike grounds over 1,000 flights in Germany - Anadolu Ajansı</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Copter Rescues Teen Stuck In Mud At Wertheim National Refuge - MSN</t>
+          <t>Lufthansa pilots’ strike grounds over 1,000 flights in Germany - Anadolu Ajansı</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 14:29:26 GMT</t>
+          <t>Fri, 17 Apr 2026 10:14:12 GMT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOQWp0N19jNjc1X3pmVUc0a3dIR1Q0dGFKRTVYOTRseWVaUkM1WWxhTTFmTGMxSW5VSXcwUlB5a3hrNm5BbUYtam1SWUR6OHROandWcXRHZGVET2JZMldRd3hsWFI3QlU1RUpBOXdidEZBaGw4UlQ0dmk3RW5Ga3lteU90ZUhXbjBlaW5oTFBzd1p5T2p2UXlaYTdnaEJPTDloUVRPcXRyaGxjNnU0Tm1uMVJHSWNYeE1BeFd4Rk1rek9kc2hC?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPOUxmVldmS0FZLVB1NTRSbm9QTnFSOGJHVW1tbGtBSVVFWHV5ajBldko3akw5MUdYbGozcWxIYks2bmhNSnBhczRRdTl6M3NpaUVTd2ttZUp3YTh3bVBRZHhTazVxWUhJLWd5VE1NQW93SFVMaVR5OWZSM2RXMUNOSEZLNVNCaEpWMWMxbWdXTmxScW4zdDlVc1lTZzBTUQ?oc=5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3160,16 +3160,16 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>DE:en</t>
         </is>
       </c>
       <c r="K50" s="1" t="n">
-        <v>46128.60377314815</v>
+        <v>46129.42652777778</v>
       </c>
     </row>
     <row r="51">
@@ -3185,22 +3185,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Stony Brook Medicine Showcased Mobile Stroke Unit and Advanced Robotic Platforms During East Campus Day Visit - Stony Brook Medicine</t>
+          <t>Copter Rescues Teen Stuck In Mud At Wertheim National Refuge - MSN</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Stony Brook Medicine Showcased Mobile Stroke Unit and Advanced Robotic Platforms During East Campus Day Visit - Stony Brook Medicine</t>
+          <t>Copter Rescues Teen Stuck In Mud At Wertheim National Refuge - MSN</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 03:13:27 GMT</t>
+          <t>Fri, 17 Apr 2026 07:43:15 GMT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxOY2J6S042dzdwUmJnajNlNWEya1UtU2FvaC1IMzdRSVRMd29qQ0xmQ0FGSzBzdHhDQ1pKeDZCX3dwb0NfUlk5b1hzSkZqTmRmOUhRTTdiektpUVNxNDZGTzRwRzZDWnkxS0JvYURSTXA1bzc4N1ZnU0Ria0lSOFFFakpuQkVFSDNEbWVXRDFZRlpqVW9qSVZiUTNodDlsbTAtMk9NMVpybThrM2hmNkRfbmJlOG5kVUc5aWdvM2pwNEdPNnd6SUt0RU12aVBUYWtKTXNyVWRDM1Ezb3JRR2FxWVluRXo?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOaEpIbEYyM2NBaTNpRmVac3BMMWR1aTJNdkY4OG1famNMbmtYTHNpSTR5b3NIR080SWQzMXlzRk85TUpRSktHQUthamllRkxLV3JWbEZDVGoxVU9DZEg4cGtYT2UwbDZFRG91akJTdXBnTVl1ZUc0ZG5xNzFiWE52dVlWV0FSS0pReDdmX2d3Nkdhb0hTX0NpenRGWHprSjdTWkJlbWJ1dzlMV2xqdlJ6U0Z0TmRVNjBqc3lQNU9kcFlpX01w?oc=5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3224,38 +3224,38 @@
         </is>
       </c>
       <c r="K51" s="1" t="n">
-        <v>46129.13434027778</v>
+        <v>46129.32170138889</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Local Town Ingolstadt German</t>
+          <t>Village Wertheim (fallback)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
+          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>19-Jähriger mit getuntem Fahrzeug: Bußgeld und Fahrverbot nach riskanter und zu schneller Fahrt - Augsburger Allgemeine</t>
+          <t>Stony Brook Medicine Showcased Mobile Stroke Unit and Advanced Robotic Platforms During East Campus Day Visit - Stony Brook Medicine</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>19-year-old with a tuned vehicle: fine and driving ban after driving too fast and risky - Augsburger Allgemeine</t>
+          <t>Stony Brook Medicine Showcased Mobile Stroke Unit and Advanced Robotic Platforms During East Campus Day Visit - Stony Brook Medicine</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 11:24:12 GMT</t>
+          <t>Fri, 17 Apr 2026 03:13:27 GMT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPdExGZUV1ZkZEVDRaak9XZlhldHpUblJtX1RXT1A5Q21MMlZGRGx6TGJ3T2pMbC13OXhhTy1IWExrLVNlbzI4dmMxbVpKWTgwc0kwbDRhbUp2dlA3Yk5nQnlnUmhkQlZoY0N1N29Yb2hVRkY0TUkwd0IzZjhXaWdSclRnbFJKU2gwekRYaU1QaWlvdDNkMkFvTGdJU1MyWTZxeElvbHkybzY5V3JFOGpXZE9UOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5AFBVV95cUxOY2J6S042dzdwUmJnajNlNWEya1UtU2FvaC1IMzdRSVRMd29qQ0xmQ0FGSzBzdHhDQ1pKeDZCX3dwb0NfUlk5b1hzSkZqTmRmOUhRTTdiektpUVNxNDZGTzRwRzZDWnkxS0JvYURSTXA1bzc4N1ZnU0Ria0lSOFFFakpuQkVFSDNEbWVXRDFZRlpqVW9qSVZiUTNodDlsbTAtMk9NMVpybThrM2hmNkRfbmJlOG5kVUc5aWdvM2pwNEdPNnd6SUt0RU12aVBUYWtKTXNyVWRDM1Ezb3JRR2FxWVluRXo?oc=5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3265,21 +3265,21 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K52" s="1" t="n">
-        <v>46128.47513888889</v>
+        <v>46129.13434027778</v>
       </c>
     </row>
     <row r="53">
@@ -3295,22 +3295,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Mutmaßliche Marihuana-Fahrt aufgedeckt: Mann wohl unter Drogeneinfluss unterwegs - Augsburger Allgemeine</t>
+          <t>Drei alkoholisierte E-Scooter-Lenker sind heute Nacht in Ingolstadt aufgeflogen - Pfaffenhofen Today</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Suspected marijuana drive uncovered: man probably under the influence of drugs - Augsburger Allgemeine</t>
+          <t>Three drunk e-scooter drivers were busted in Ingolstadt tonight - Pfaffenhofen Today</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 07:32:48 GMT</t>
+          <t>Fri, 17 Apr 2026 11:36:11 GMT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwAFBVV95cUxQWEViLTRERjFOOVZzZkJiWmRVbmtjU2lySGtpWjE0Q1JVak5udnRsU2JJQVJEcWtsNHFHRldUakF4ajhfN1l5MFlET3V1RlZNYTQ3Y0NnczhScFc3dS1QQk5tb0paVm92eDlRSU1JejRyV3hLbDFWVjJjcXlBcjhROFVmdGs4eU9VeGFlREVBZ0hLV3ByN2c4MDRQUEZfeEZqUDN4Vm9ILUlVRVJ3ejA0emdjU0VHS0pZMTQ3OVJMSS0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxNdXg2S2NVWHRRX0tMSUhxLUJQTThROUk5MlpJTzFGUzRncDQzbFVPNmxFcWZNdS13ZnBoc0IyUWZGdE5FQUxxbnpMYTVKMTZBTDRRTE53NXFoZjItVGJ6MzNuOUtTdVNqaWtrYnlSY09fV3g3S0lBY050ZFVyU2VQN1Vobk0xcDBEa3c?oc=5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="K53" s="1" t="n">
-        <v>46128.31444444445</v>
+        <v>46129.48346064815</v>
       </c>
     </row>
     <row r="54">
@@ -3350,22 +3350,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Streit nach Unfall eskaliert: Radfahrer schlägt Heckscheibe eines Autos ein - Augsburger Allgemeine</t>
+          <t>Kreuzung nach Kollision mehrere Stunden gesperrt – Zwei Personen verletzt - Augsburger Allgemeine</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Dispute escalates after accident: cyclist smashes the rear window of a car - Augsburger Allgemeine</t>
+          <t>Crossing closed for several hours after collision – two people injured - Augsburger Allgemeine</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 11:34:13 GMT</t>
+          <t>Fri, 17 Apr 2026 08:41:00 GMT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiyAFBVV95cUxOUkxGVTgxNVJQU0p4dkg2MHgtZmdsNmc5d0ZjVGJEWFZ3WmhHbTkwZDB3S2MtREtoU0ZYYzQ4aGIwNi11Y3BwdEJsaDhCZldfd2d3WktBT3pWQ0FRNEdBTllrWUVSVngyR2NZUUczTUo0dXFQaUh2cjNSX09QczNmWGN3RXM3ZW9DYWNUYmJoVE9Jc2ZvVjlUZklhLUluTHM1NjQyR1lNSVB2UTBiczRvZVl6S0s2d3hZM21zMldMbjZWaU5Vc3RCTw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiywFBVV95cUxNUmN5Y0tSZHo0TDVtNkVhcXZNQ2tjcGRnb3RFWUFxYkJJRmdBa3VPRVlScGdabXFJdTNSakdyWEFaRURoUThQRkp0TmMyd0ppMGRMeUtNSFhVVXdxb1FwbjZneVJ1eS1hNVVUUVJoS3AzVnBMZHA4YnVKcXlaZVBidDR0NElqd0tNNXdjN3FJaXVrVl9CeUd1eGczcUxoZGg1ZjZELVBRcnhzTnNOQ3F1YjhPTUZxV2hlZHdSQm1qa0VLUUEzbnpNLVJVQQ?oc=5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="K54" s="1" t="n">
-        <v>46128.48209490741</v>
+        <v>46129.36180555556</v>
       </c>
     </row>
     <row r="55">
@@ -3405,22 +3405,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ingolstadt: Aus Zorn nach Unfall: Radfahrer schlägt Autoscheibe ein - STERN.de</t>
+          <t>Stein vs. Carmona: WBA title fight in Ingolstadt - boxsport magazin</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Ingolstadt: Out of anger after an accident: cyclist breaks car window - STERN.de</t>
+          <t>Stein vs. Carmona: WBA title fight in Ingolstadt - boxsport magazin</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 09:56:32 GMT</t>
+          <t>Fri, 17 Apr 2026 08:27:22 GMT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMizAFBVV95cUxOU3FTYVBHcWFjdlhmZ1RLV0JhYnFvcmtoLW5KQ3lrTVdqSzBqX0JqNmJ2dkdNNGpPRjhqN0xBS3MwSzMwUU1ZRUlnMWExdERiTTBzOVJycHRpa2JDUWdrbkh4RTFZS3pwd05lbmFjYUctZGtMV3ZxSTRPOUNHR1NpSlYyaVlMcFgzbHhVR1cyQk5SS00wS0V0OXNtaDVhanRoUXBxY3I0NnQzOVIyVXdaNDBlaEpqS1ZLbWtqc1pReWVWeHZyRXh1SmZZNzA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQbnFBTGo2RTAxSlpXcHpQQ2VHc3ZFaXZLd1h0SnlZdTExMUNXa0R3dU1EZ0g3UnV1UC1LRnJ5aW9Dcm9OaEhyWjhXRFN4VnloUVRsTFcwT2lkZHV4UUdWUi05bDFUQWtXTmROWE5wUWYwdnR4dW95em9qUkp2VzVDUE9B?oc=5</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3444,38 +3444,38 @@
         </is>
       </c>
       <c r="K55" s="1" t="n">
-        <v>46128.41425925926</v>
+        <v>46129.35233796296</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Village Las Rozas La Roca (fallback)</t>
+          <t>Village Bicester Kildare</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>("Las Rozas Village" OR "La Roca Village" OR "Las Rozas" OR "La Roca") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Bicester Village" OR "Kildare Village" OR "Bicester outlet" OR "Kildare outlet")</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>All Costco stores to close for 24 hours this week as shoppers make other plans - MSN</t>
+          <t>Four Seasons Hotel London at Park Lane to unveil new suites - Boutique Hotelier</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>All Costco stores to close for 24 hours this week as shoppers make other plans - MSN</t>
+          <t>Four Seasons Hotel London at Park Lane to unveil new suites - Boutique Hotelier</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 11:03:45 GMT</t>
+          <t>Thu, 16 Apr 2026 13:59:30 GMT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wJBVV95cUxPUkY0UEY5Z3FlYXV6VUJtTURHOHgxOVNvNFNpVzRTUk5hNERQSnc3bTNpTlpCMEhKZjZLNVFKUjBUX2doSHlNQWFkb0JZdjB6cEdHTDU3cGViV0RWWUtCMVNTd3lYYUFYLWdkQlRmVlpxYlRXXzEzSmxEYlpsdFg1bl9RWU1yOHJmUVhXR3RMQ1FGWGsxR3I3Ti1Na0FqaXN1TjJUNEFWdTFIdVFOb1lnRUNkTUJvU24yRFZtclQxc1dGVjBqNlBaRldnZ2hiZnRWSjNyWjdfWTZ4RFI0MDAxZ2RrM3ljNkZVVjlZeVhNRkdwMlNHRHZMZnF4eE96NGQzM3haOFpZcHplckgyMmFJTWVxSzNpUG9FTE9OY2dFaWQwOWI3Q3hrU1d0UmpXS05jVDgwTHpjNjlBTUc4UHhySERtdVlOZmNtX3BaczZ5M3QyRFFlc3pZOVJRTWpVX0hkb2ww?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxQclRxWnp0aDlycHJTSlZOTUxEcnBBR2FCa3dnSDhDUHVnOVhSMVpGMS1TVFlaM09CRGRzdXByVk1kanZLY1JfUUlWNkRTNEpqS05lUDJLQVdEV1doSFluQ0t1dngzZHdLdXhkOTJ1VGZ4ekdSRzV2Wkd5WFNJM1A1ZFZRQ2VybHVxRldOcDFCd1Y0TVlPT2xLTQ?oc=5</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3499,7 +3499,7 @@
         </is>
       </c>
       <c r="K56" s="1" t="n">
-        <v>46128.4609375</v>
+        <v>46128.58298611111</v>
       </c>
     </row>
     <row r="57">
@@ -3515,22 +3515,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Killer found guilty following stabbing in West London - RailAdvent</t>
+          <t>Epsom protest organisers ‘reassured’ after private meeting with police | ITV News - ITVX</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Killer found guilty following stabbing in West London - RailAdvent</t>
+          <t>Epsom protest organisers ‘reassured’ after private meeting with police | ITV News - ITVX</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 12:15:00 GMT</t>
+          <t>Fri, 17 Apr 2026 08:03:57 GMT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOd2dzaW1oa3lvZTI2djdIX01SdjhxdzBSRFMxaGk3eS1BeVg5VmlESUpVS09Db3RoMzdoaXZZR3RETC14ZHZPYnpoaGp6QkJGUmQzbFZ0cUhJVDl6NXhZUlJlRi1EZmpGdDFSbTdiU3BCVHI1WVdTU1M3OF8yZVVOQVIxVGtNR0V4U2FwamR0b2hQZlE2WDU5Nm42Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMisAFBVV95cUxPc1ZzeVdyRVFJVmltTVo1NVZPekJhSWltVWNuZ0w5QkZlWHA2Y2VHd215WE9wU0FyRlViR01ycEV1N184WVNaMmxLMDgzRWVqRnBDcUhfZVR6Z3IzdU85SS02cWs2am42cnJNTTZYdFdiVlh1WjVoX2RkX3NZcnpZT3FYS1VjelVsbnU1YzFsNWFCa0RyYXhpZVZiRzFqTHpaeXBGSDFsd3pkVHkxcHgwOQ?oc=5</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3554,7 +3554,7 @@
         </is>
       </c>
       <c r="K57" s="1" t="n">
-        <v>46128.51041666666</v>
+        <v>46129.33607638889</v>
       </c>
     </row>
     <row r="58">
@@ -3570,22 +3570,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Russia issues bomb threat to four UK locations including London, Suffolk and Leicester - lbc.co.uk</t>
+          <t>Two appear in court after Finbar Sullivan, 21, stabbed to death in Primrose Hill - London Now</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Russia issues bomb threat to four UK locations including London, Suffolk and Leicester - lbc.co.uk</t>
+          <t>Two appear in court after Finbar Sullivan, 21, stabbed to death in Primrose Hill - London Now</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 14:46:05 GMT</t>
+          <t>Fri, 17 Apr 2026 10:45:25 GMT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1CVVFFeUtVejdKSmNuYkpKZHJ1OWItSnpFLUM4VTVMSzMwWkNiLV9RN0tFN0pPNXJPU29POTVhZnNmTmlucU5uYUhEZ0xnWUZ6bjlvbE52R3hnNU9BdF9fbGRmWm12MjItYzNFQ0FuMmZqSDZQVmowcy14YlQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxQbGU5UFJKSjZ2ZjBMOW1WVVJNX1kxSXkzcE4zeUc3VUNOd1ZZZEEtRHg0Rk5wTC1MM2xKanFDUDF0NnpCTkxiSmVTU1IxOHhfUzU0SGs4N1YtLUZieUY0cnFpM0hyX1ktUGl1VEVKVUN3dXNUem1ZekNncFBZTG01cmtEdmpXd2FGLWhvb2F1Z0pXZnoyTXktRGZXdmVwRnpydl9j?oc=5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="K58" s="1" t="n">
-        <v>46128.61533564814</v>
+        <v>46129.44820601852</v>
       </c>
     </row>
     <row r="59">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>LIVE as motorists expected to protest fuel prices at major M25 crossing - London Now</t>
+          <t>RECAP after motorists expected to protest fuel prices at major M25 crossing - London Now</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LIVE as motorists expected to protest fuel prices at major M25 crossing - London Now</t>
+          <t>RECAP after motorists expected to protest fuel prices at major M25 crossing - London Now</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxObXVNVXptYl9hU0VXY016NkwySzZaSm96OG5QTHY4Qm9JTG9zeGJqSDNzVjVucy1wcE5Ud0cyeExaUEpnWl9jZUpiR0NxRTM5b1B1ZnRMV1ZfY3QydzA4dWl2YktmQTByOXVmWlFZNm5iOUZYOXVYOHkxS0dhaWM0UmpMVGFHVjNFREpqLTV1T2ZFWllrenQtUGtCckp2WlRTMy1MVk9B?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQc280YU9hMEdTemJiLUVuU2x4VWVoc1JOeWI1Q0lnRjB0dkxBYm1WUUg4VTkwekV5ZU5aZjdZTEVKaG9LX0I4YnFkckVjemVQcTYyVFZBTm1VdXlRaUZ1UUY2THpnV1VHcFpGYUtJOENVckxaVlFyOHotMGxucE5Ydlk1VzB1OS1EdjE0Z0RmNXVGb0N1OWIwWEpVWUY?oc=5</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3680,22 +3680,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Why are fuel price protests sweeping the Republic of Ireland? - Al Jazeera</t>
+          <t>Met Police accused of 'dark and biased' over pro-Palestinian protest handling - London Now</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Why are fuel price protests sweeping the Republic of Ireland? - Al Jazeera</t>
+          <t>Met Police accused of 'dark and biased' over pro-Palestinian protest handling - London Now</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 09:54:26 GMT</t>
+          <t>Fri, 17 Apr 2026 07:52:53 GMT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqAFBVV95cUxQMDZQYUNzU3JOemFGZmJ6alJQaHZqVUVlQTVnSzBrSl9BZS1sekNSSEdQT1hrY3E0YU8yUVQ5TnJoaVFXSDdWdm93U0I0dHZQQTV0SVBYVndhUDdvN2QtV3p0RE40MEJNa0Q1QWRxR19XakE5UElGQWxtYU54V3otTmpud3ZxN3pvVWVEU1BkejdEbmdISEIyX1ZUak4xTmpuRWxxeXJOaWHSAa4BQVVfeXFMTjI2SEFuUDdzREtzSEdDRHhUcjlBRnR4UXNYSnRLelJMZmliRWRoWW1SQm1WZ3ZkYkZGYjBHaHRlMnBTV3RsdHhuYk9neF9EMlZ5WENuYUF2enV2eEI4OWN0T2xQRGtubEZ0dUpaMjdZMXh2WUt5cm9ERWNGcXBuSjFtWkk1YjE2dU1UVGlXczQzMlE3cVBJdWpuTVo1U0NxRDgwazVfVXZCcjdZQzBn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPSEZVdzVvVXNuUklLWDdtUkVSb2VMNXcyRDgxY0p1Ty1MN2l6YUlUN1lERjhNQ1ZIMkJVdjhTekM1aXhiQTVSTHc5NG9VUzlBcnQ3WFFSdG9MQTRCbG1WVHNXenFpZW9wQzMyS05la0k0bFRoYXU1N2V0b3VQM1VlLVM0MWZrRlZ1Yjl2ZUt2eDdxNWhOczc4?oc=5</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -3719,7 +3719,7 @@
         </is>
       </c>
       <c r="K60" s="1" t="n">
-        <v>46128.41280092593</v>
+        <v>46129.3283912037</v>
       </c>
     </row>
     <row r="61">
@@ -3730,27 +3730,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
+          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>London bus turmoil as TfL workers vote to strike over rota changes - Unite the Union</t>
+          <t>Russia issues bomb threat to four UK locations including London, Suffolk and Leicester - lbc.co.uk</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>London bus turmoil as TfL workers vote to strike over rota changes - Unite the Union</t>
+          <t>Russia issues bomb threat to four UK locations including London, Suffolk and Leicester - lbc.co.uk</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 09:49:13 GMT</t>
+          <t>Thu, 16 Apr 2026 14:46:05 GMT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwgFBVV95cUxQcVlaUEduaTUtZ0J3cDhOa09hNHVBODdWUlNHZ0FNb3VBSXgzTU9HV09qZ093V0swdXBsV0s0MUVDQnh4YnlKOHNDRXdBWlEydnFzU2FGQ0dSRjhDVFRFUDZkTGdYTk96ek5RUENQdHM3TkRDVTlVTHQybjlUMUlTNUFMWnUySC05Y0x5VGZaUHRQdDRTSjZEdEYtY1U3Y2htQ1pOSG12S21KR1J5Nm01ekp6eUQwUGVueGtxNGhGUTJUZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMifEFVX3lxTE1CVVFFeUtVejdKSmNuYkpKZHJ1OWItSnpFLUM4VTVMSzMwWkNiLV9RN0tFN0pPNXJPU29POTVhZnNmTmlucU5uYUhEZ0xnWUZ6bjlvbE52R3hnNU9BdF9fbGRmWm12MjItYzNFQ0FuMmZqSDZQVmowcy14YlQ?oc=5</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -3774,7 +3774,7 @@
         </is>
       </c>
       <c r="K61" s="1" t="n">
-        <v>46128.40917824074</v>
+        <v>46128.61533564814</v>
       </c>
     </row>
     <row r="62">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>What is needed for next week's London Tube strike to be called off? - Metro.co.uk</t>
+          <t>Hundreds of police officers drafted in for Britain First protest in Manchester - The Independent</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>What is needed for next week's London Tube strike to be called off? - Metro.co.uk</t>
+          <t>Hundreds of police officers drafted in for Britain First protest in Manchester - The Independent</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 05:00:00 GMT</t>
+          <t>Fri, 17 Apr 2026 12:00:00 GMT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxNV2lJSkNaTjFBQWpLbU1LTVltdXpyeUdUUXNUX2RTczEyLVpTeTljemtQdVRwUXdkemRQVUxHbEZQQmxKUXV5dE5xNHhQV3NpTldNOVdPSk40bGxnc005bTllX2dfRmRCdGJiaGtKYVpVeUpDV1ptSjE1cTk3ZHUyS2ExYmtHWmRMd0o0dF9xMjNId9IBlwFBVV95cUxQQXVJYjlHaGo2cTUyMGNpUjM3R09icWF5bTQ1Wkh0ZHExeVhWSTdaZGpjaVlMT1AzQUdnbWFpMVVCYWpYUkpjRHVVT0lxNVVxOFAwNllzNmhaYmZ2LXg5QTUwLUs1c0Fic2hpbmtNTXVLTFJraXE5amtkcUhfdnVRN1k1cHU1aGRvTlB5blVlZ0h1SFZVT2Rj?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiowFBVV95cUxPbmZRYmpJTV9aWkpoZmVFVmdzd01CLUFLZGQweGEwckJIYnVoam1iX0dKLXFPektUUWx0VXFkZDQweXNjOEZyd1Vud0xzUTl0bmQzYUVRVlVyRmp3RUhoTkNKT0VnYnE2OTYyd25Ec2ZNS2NiVjQ1ZG12aVZhVkxnM0NTTDFMMXNhR1ZuWFptZ0FUWUFtY2JRTmVYTDkyOXB0Sk5F?oc=5</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3829,7 +3829,7 @@
         </is>
       </c>
       <c r="K62" s="1" t="n">
-        <v>46129.20833333334</v>
+        <v>46129.5</v>
       </c>
     </row>
     <row r="63">
@@ -3845,22 +3845,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sharon Osbourne shares plans to attend Tommy Robinson rally in London - London Evening Standard</t>
+          <t>London Tube Strike to disrupt services next week - RailAdvent</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Sharon Osbourne shares plans to attend Tommy Robinson rally in London - London Evening Standard</t>
+          <t>London Tube Strike to disrupt services next week - RailAdvent</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 16:24:11 GMT</t>
+          <t>Fri, 17 Apr 2026 09:16:00 GMT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPWFc5ZDBBVy01NEh5Y0pPODZWZWhZdDFUd2J4OFpQZkZoaURydU1CZE51MU9Ka2NaLWw2S1NHcTRKTERVWVMwVmdDNl9CLW5mTS1kbDZPdlJ1RC1QYXFuRjgzSDNrS0FmU2plb1l2RkxLSmZMVjl5Q0V1Q0xrc280UXpwbFZpdHRiUEZYbDlvVmVPaC1tWHRB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxNQkRFOUw0UFB1QVFzS05XQWl0dTFXSXVGRDFXakJJZy1rWVhHT2QwYlRxT2czaG5rUVUxb0Fob0VFcmRfa1hZOFhNZnA3aDhtSVh5cWRCX01SMGo4bHMyUHNfMHdDT0g1UkdBN29WWWZaa1Y2Zi1fN3I3T0wzYVZSaGtMcXlTb19MbHdnZ0haVllaMUVh?oc=5</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3884,7 +3884,7 @@
         </is>
       </c>
       <c r="K63" s="1" t="n">
-        <v>46128.68346064815</v>
+        <v>46129.38611111111</v>
       </c>
     </row>
     <row r="64">
@@ -3900,22 +3900,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>London mayor dodges Nakba march dispute between police, orgs - The New Arab</t>
+          <t>Britain First to march through Manchester tomorrow as police issue statement on huge operation - Manchester Evening News</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>London mayor dodges Nakba march dispute between police, orgs - The New Arab</t>
+          <t>Britain First to march through Manchester tomorrow as police issue statement on huge operation - Manchester Evening News</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 15:08:40 GMT</t>
+          <t>Fri, 17 Apr 2026 12:00:00 GMT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOZVI3OTVhTG5Ob2tSUTJrSG5ZTjNmc0ktWEF4dXh6dnBEcHpQZXczUUU4SlRYVzJFMm1WUUtranRGOWM5YS1FbWIyOVRvUXB5cmJMRl9TVG9vd2pCU3Nqczk5QWYwdC1pRC1FSXJESm03VS1Pby0wMEl3ai1yRS1JcHRTQ0FVOEZseXdabUpGTm9JZ9IBlwFBVV95cUxNdTN1RFRaN1BUQUNWSEFtTGdURWozd2NySFhGQnU1ZTB3cS1QX2ZfcmZFX29lU29PTURjRG81aXFLcE9tbDNCajJRZnlkZFRKbDdSUU4yRzhrZ3hNT0FqNEMtRVRzWEkwZjdwZWFJQzZCV0JkTWpoMWpxaXRKSkszRFhTdDhpUGlkdXVaQ01Wb1ZLVzdWWDFR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxOYXA0bEs4cFdFNjl3NEpJejNVczlrTklFS0lSa252cVlnd3VyOG95VzRwR1pOTDhKUEhOeUoxLUhyMU04N1RTeVZsd1pWSkFlZUlQdmJIRXpjb0NBY3JiSVRWbUFRekVaenUzMXItWk8xYVc0c3U2dUN4dnNKdnUzVG1MQU5KN2RsZTZqQ2Z5N1R4N0E0aENMaVZwM3IwLWxCOF9xWVEzaExRdTJfNkpqRHZkUWVOd9IBuwFBVV95cUxQWEw0b1VZTHlrZFpCYnE2QkRoend4a2hZa2REeXVsWlB4WUJXS3dFSmVDODhENWhtc01lR0M2eWVnWlhTQ0d6TTVzLVI5VERtUEp2dHRiX1ZZLVk1RjVBLTdqVV8xX09VSXlNbXZRUzR3TW40YlhndVJOTThyMjNZLXhZNG5fcnFEaVBaUW96M09jbkVjTDBKeWlLVkNfbC1FVkNWakFEV3NMekRueEMyM0MzRFE3N2tTUUxv?oc=5</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3939,7 +3939,7 @@
         </is>
       </c>
       <c r="K64" s="1" t="n">
-        <v>46128.63101851852</v>
+        <v>46129.5</v>
       </c>
     </row>
     <row r="65">
@@ -3955,22 +3955,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>50 Holocaust survivors from Israel and around the world to lead the 2026 March of the Living alongside survivors of antisemitic shooting attacks from the US, UK, and Australia - EU Reporter</t>
+          <t>London mayor dodges Nakba march dispute between police, orgs - The New Arab</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>50 Holocaust survivors from Israel and around the world to lead the 2026 March of the Living alongside survivors of antisemitic shooting attacks from the US, UK, and Australia - EU Reporter</t>
+          <t>London mayor dodges Nakba march dispute between police, orgs - The New Arab</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 07:16:04 GMT</t>
+          <t>Thu, 16 Apr 2026 15:08:40 GMT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi1AJBVV95cUxNeXhrTUZqaWEza3RaS1VEWXM2RUZjMm0tRFF0cWhvTnFsRTd4cEJOOEZodDNVRmd5N09heXUtQ1FDM0ZBSkFMNTlJbzJfMEZZS1ozYjFzM0lybDdQSVBGZTFCSEphSTA1Y3F6X0tsYzR6cjUwSHVEdks2QW1rektueV8zbTRLaXRBUTQzdUd1akJtdkFVWnZxT0RGaFkwYTljNFM4blJQaUNLUVZDNjdQcWZiaEpheDNYOWpJajJaUlplYlNubGRPdkhfZkNHVWF5UU1DcG44NzdWZWFjWVl1MVZ2V2VGTlgzcG5nLTBzQVE2Ri1YbDZRLXNzQ0pZTjg4WVp1N1YxY1ZoeVNsV3lyMWxpc3V2LTFRQUpaU3h6R3JpaFNDaHNLR1VZWE43VXJiVExLTWtyVzROMlhSXzlSY1lMSnlnMlJ0QlFCMVo3Mk1VV3hy?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxOZVI3OTVhTG5Ob2tSUTJrSG5ZTjNmc0ktWEF4dXh6dnBEcHpQZXczUUU4SlRYVzJFMm1WUUtranRGOWM5YS1FbWIyOVRvUXB5cmJMRl9TVG9vd2pCU3Nqczk5QWYwdC1pRC1FSXJESm03VS1Pby0wMEl3ai1yRS1JcHRTQ0FVOEZseXdabUpGTm9JZ9IBlwFBVV95cUxNdTN1RFRaN1BUQUNWSEFtTGdURWozd2NySFhGQnU1ZTB3cS1QX2ZfcmZFX29lU29PTURjRG81aXFLcE9tbDNCajJRZnlkZFRKbDdSUU4yRzhrZ3hNT0FqNEMtRVRzWEkwZjdwZWFJQzZCV0JkTWpoMWpxaXRKSkszRFhTdDhpUGlkdXVaQ01Wb1ZLVzdWWDFR?oc=5</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3994,38 +3994,38 @@
         </is>
       </c>
       <c r="K65" s="1" t="n">
-        <v>46128.30282407408</v>
+        <v>46128.63101851852</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>High Level City France English</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>("Paris" OR "Île-de-France") AND "France" AND ("bomb threat" OR "suspicious package" OR "shooting" OR "stabbing" OR "terror attack" OR "police operation" OR evacuation) AND -Texas AND -"Paris, Texas" AND -film AND -movie AND -football AND -transfer</t>
+          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PA said to extradite to France key suspect in 1982 Paris antisemitic terror attack - The Times of Israel</t>
+          <t>Sharon Osbourne shares plans to attend Tommy Robinson rally in London - London Evening Standard</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>PA said to extradite to France key suspect in 1982 Paris antisemitic terror attack - The Times of Israel</t>
+          <t>Sharon Osbourne shares plans to attend Tommy Robinson rally in London - London Evening Standard</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 15:42:00 GMT</t>
+          <t>Fri, 17 Apr 2026 02:27:44 GMT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPQ0NLY0Q3WENUNy1XUE1yZVJVc3htTXZPU3VMQ29EeVZzbnBnOTVCM3ZNU2IxZWllRE9peGlrb0l0VFZDaXJBeENjbWFWZ0RVazdGYld1a2pxT2g1cVFKSEZMUldtcGpET0RBNk85eTFHVFo5UXVQMlRjMnJLOHFuUndieHdITHpBV2xELW5qZ0JmUU5WcTJucXJCTVNYR0ozVHBOcVhUZ19fc2E0alZMTlV1UdIBuAFBVV95cUxPc1laRDlVVUJGUnROcWZUZWMwcXBjMW0tZ2V5TzZ3a3VLQ2VLeG1JNk5tTzdvWC1TWnZaTVdNSGhQNG5zc1dzSURWTGpsQTFzSGh4M3NvcEVuM1lWeGNOZ25naS13VlpSQUtnSDBveTcxM2dYRjNxWlNTVFBHaUt4WDc5SXRiTHo5QXVHQ3A1UzlQOUpCTTJ5UHRJUENIUXlIczNhN3RSNUtQZk5PX3hMRGFfa1UxVE5J?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxPWFc5ZDBBVy01NEh5Y0pPODZWZWhZdDFUd2J4OFpQZkZoaURydU1CZE51MU9Ka2NaLWw2S1NHcTRKTERVWVMwVmdDNl9CLW5mTS1kbDZPdlJ1RC1QYXFuRjgzSDNrS0FmU2plb1l2RkxLSmZMVjl5Q0V1Q0xrc280UXpwbFZpdHRiUEZYbDlvVmVPaC1tWHRB?oc=5</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4040,47 +4040,47 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>FR:en</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K66" s="1" t="n">
-        <v>46128.65416666667</v>
+        <v>46129.10259259259</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>High Level City France English</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>("Paris" OR "Île-de-France") AND "France" AND ("bomb threat" OR "suspicious package" OR "shooting" OR "stabbing" OR "terror attack" OR "police operation" OR evacuation) AND -Texas AND -"Paris, Texas" AND -film AND -movie AND -football AND -transfer</t>
+          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France prepares for terror attack hitting London amid Donald Trump Iran war tensions - London Evening Standard</t>
+          <t>Epsom rape protest: 'Stay away,' Far Right crowd told after clash with riot police following attack outside church - London Evening Standard</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>France prepares for terror attack hitting London amid Donald Trump Iran war tensions - London Evening Standard</t>
+          <t>Epsom rape protest: 'Stay away,' Far Right crowd told after clash with riot police following attack outside church - London Evening Standard</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 11:57:35 GMT</t>
+          <t>Fri, 17 Apr 2026 07:35:38 GMT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPeFY1WF9FUm1jTC1FaEJCcXhma3k5SndZX0JzSDcwSW03bmJFb24tLVRYaFlLY24xbk4yWm9jMkRhNkpHYXpxZzlPODNVV0R5SjZib2dQMmlTVzRVbVpqSWZKdHNrTzN5Yk1aZDY1ancxNm5Mc2lUdThLTlkzWmh5US01OEh5OUJucXhPMWRtN3Y4WXBISXlQTVVsNUdaajNHVFhhUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxQUWF1bW5ybFY4cF9qbG4xWXJKMXgybXl1S2VuZV85V1ppV0JLdDJoVFlxb3hRZjlwaXVoLTBuYkNEQXdHMjlCTHRsT3RQMHpHSEhqVEczYkFmMGhqd1g5djY0aDU1ZGdOUUx1akh4Q29abnJhMVFDUXZsc25NSXdUakZCeEEwcVVPdzBHaDNB?oc=5</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4095,47 +4095,47 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>FR:en</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K67" s="1" t="n">
-        <v>46128.49832175926</v>
+        <v>46129.31641203703</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City UK Ireland</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Oxford" OR "Bicester" OR "Oxfordshire" OR "London" OR "UK" OR "England" OR "Britain") AND ("protest" OR "demonstration" OR "blockade" OR "strike" OR "march" OR "rally" OR "civil unrest" OR "disorder" OR "dispersal order" OR "anti-social behaviour" OR "flash mob" OR "social media gathering" OR "link-up") AND -sport AND -football</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sciopero dei bus a Milano (e non solo), a rischio gli interscambi: gli orari dello stop - MilanoToday</t>
+          <t>Strait of Hormuz blockade: France and Britain to chair meeting again on re-opening crucial waterway amid war - Deccan Herald</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Bus strike in Milan (and beyond), interchanges at risk: stop times - MilanoToday</t>
+          <t>Strait of Hormuz blockade: France and Britain to chair meeting again on re-opening crucial waterway amid war - Deccan Herald</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 04:15:22 GMT</t>
+          <t>Fri, 17 Apr 2026 10:52:59 GMT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMidkFVX3lxTE1ncFU0Q2hBaHlMUF9kaGZ1U1FGOGNsNjVYdHVTWnB1bWhCQmRQWEdxUHZrQi1nWnFYdHpXdHV6czd5WXJFNDNOYjdOV1lNV3RveEFPWHRJbTI4OWxFLVE0dXNWQV9DYTdObEJWc0ZmQUNJWVd5eVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi9AFBVV95cUxOcVNDWjdMb2FnMXFlT19oWC1jV3FfWkFMZ0x6dHNLVExIM2ZRcUx2VTFiVmxNcHpBUTNsTm45YkJEbHBTTG5uc0owcnlTWHZrTlZXdno3c0RCXzhlNnY4MFVMc1A4UkVNbnhZcHBVREVpMFktd1U1ZWw3RlA5ak8yZjJ3NzR3R3p2UElCY21xNU5hSC1jNWltRTlmTkZyb3BYQzJQQzl2SEUzQkxuRGZUQlZBR3NIT2ZDU3JxaE0xeDJIb2l4c2I3dXNWZ25vYk1PVWxlNFg2SFQtWGNhRW12SVp4SFotLXM3YmdaQmloQkZJelg0?oc=5</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4145,52 +4145,52 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K68" s="1" t="n">
-        <v>46129.17733796296</v>
+        <v>46129.45346064815</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City France English</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Paris" OR "Île-de-France") AND "France" AND ("bomb threat" OR "suspicious package" OR "shooting" OR "stabbing" OR "terror attack" OR "police operation" OR evacuation) AND -Texas AND -"Paris, Texas" AND -film AND -movie AND -football AND -transfer</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lega in corteo sabato a Milano, Conte: «Sarò in piazza per lavoro e sicurezza» - TrevisoToday</t>
+          <t>PA said to extradite to France key suspect in 1982 Paris antisemitic terror attack - The Times of Israel</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Lega in procession on Saturday in Milan, Conte: «I will be in the square for work and safety» - TrevisoToday</t>
+          <t>PA said to extradite to France key suspect in 1982 Paris antisemitic terror attack - The Times of Israel</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 04:02:00 GMT</t>
+          <t>Thu, 16 Apr 2026 15:42:00 GMT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNSy1XanY2eHlnYUxHVGc5cHNSS3B5WThyZ3NHdXdCUzNRTE1Oa0l2eWcxam51ejVGTlAxSW0xQzBza1dJY1d6YWhTVXRUenV2ck13aFVoam1IZ3pTLVlwRXBhUDNOS2lxNE1EYWZGQk9rNUhUemNjUWhiaG9nc3I1VnRWVFVKSXZGTVI1aXAweHFZaVVsZHk1Sm4tMWdrMXpP?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiswFBVV95cUxPQ0NLY0Q3WENUNy1XUE1yZVJVc3htTXZPU3VMQ29EeVZzbnBnOTVCM3ZNU2IxZWllRE9peGlrb0l0VFZDaXJBeENjbWFWZ0RVazdGYld1a2pxT2g1cVFKSEZMUldtcGpET0RBNk85eTFHVFo5UXVQMlRjMnJLOHFuUndieHdITHpBV2xELW5qZ0JmUU5WcTJucXJCTVNYR0ozVHBOcVhUZ19fc2E0alZMTlV1UdIBuAFBVV95cUxPc1laRDlVVUJGUnROcWZUZWMwcXBjMW0tZ2V5TzZ3a3VLQ2VLeG1JNk5tTzdvWC1TWnZaTVdNSGhQNG5zc1dzSURWTGpsQTFzSGh4M3NvcEVuM1lWeGNOZ25naS13VlpSQUtnSDBveTcxM2dYRjNxWlNTVFBHaUt4WDc5SXRiTHo5QXVHQ3A1UzlQOUpCTTJ5UHRJUENIUXlIczNhN3RSNUtQZk5PX3hMRGFfa1UxVE5J?oc=5</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4200,52 +4200,52 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>FR:en</t>
         </is>
       </c>
       <c r="K69" s="1" t="n">
-        <v>46129.16805555556</v>
+        <v>46128.65416666667</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City France English</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Paris" OR "Île-de-France") AND "France" AND ("bomb threat" OR "suspicious package" OR "shooting" OR "stabbing" OR "terror attack" OR "police operation" OR evacuation) AND -Texas AND -"Paris, Texas" AND -film AND -movie AND -football AND -transfer</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Giornalisti in piazza a Milano: in 200 al presidio Alg per il rinnovo del contratto e condizioni di lavoro dignitose - Radio Lombardia</t>
+          <t>France Takes Custody of Suspect in 1982 Paris Terror Attack - streamlinefeed.co.ke</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Journalists in the square in Milan: 200 of them at the Alg protest for the renewal of the contract and decent working conditions - Radio Lombardia</t>
+          <t>France Takes Custody of Suspect in 1982 Paris Terror Attack - streamlinefeed.co.ke</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 15:24:47 GMT</t>
+          <t>Fri, 17 Apr 2026 08:11:41 GMT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi7gFBVV95cUxPQjc2OHdoSHdSa0tsQXU4dzVvNGdfY2pEM1U0a3Y0Z25IdDk1QkI1MUdOMWF1cWtMMjdHZnMtZy1tUTQyR25IWURUcnZuUnpkMTNKVjJuWmkyRXA4Rm96UVRYbDVDeDJnOTE1VzYtVEY0RURNenhoLV9hUUdBX3NMemR0blBzdFltQUJxa2lfckFmdzNlRDF0NEZlTTIyVC1FOU9BSVhibU1fMS1JYjVCSlVIVjk0ZmxMVW1oZzVOTlFRRE5ERl8wbnk3TkNHWHZpTF9QY1QtOU9Bc1d2X1JoYnRpRlFxTW9VRXpQQlZR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimAFBVV95cUxPbWhNNmtUZmpzYU5UVWhUMzFHcjhROURwUmJmQ1lleXpuOFBCa1JrX1BWNFJZaXlKT2tvbDNFYnQ4Y0wzWm5sMmVudnZMNG1GYWlLNno2bmY5UlFVbDV6bmRJcnNNN3dyXzJMQjA0ZkFGOS0yZjBxOXJ2TTdHQzNRYXVPdURINWNmczZmbm96bnRTN1c3emc1Tg?oc=5</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4255,52 +4255,52 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>FR:en</t>
         </is>
       </c>
       <c r="K70" s="1" t="n">
-        <v>46128.64221064815</v>
+        <v>46129.34144675926</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>High Level City Italy Italian</t>
+          <t>High Level City France English</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+          <t>("Paris" OR "Île-de-France") AND "France" AND ("bomb threat" OR "suspicious package" OR "shooting" OR "stabbing" OR "terror attack" OR "police operation" OR evacuation) AND -Texas AND -"Paris, Texas" AND -film AND -movie AND -football AND -transfer</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>CGIL: manifestazione remigration a Milano contro i valori della Costituzione - Affaritaliani</t>
+          <t>France prepares for terror attack hitting London amid Trump Iran war tensions - London Evening Standard</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>CGIL: remigration demonstration in Milan against the values ​​of the Constitution - Affaritaliani</t>
+          <t>France prepares for terror attack hitting London amid Trump Iran war tensions - London Evening Standard</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 14:30:32 GMT</t>
+          <t>Thu, 16 Apr 2026 17:34:41 GMT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxPVzBBZDRkdVRBRzE2dU1Td0MxMFBpUXZfSkU5ampLSDhTNXROR1c2MURoS2NkSDZoblFMVzVsQnllWGpUNmlXekMzZFZwUnM1eVlRQlNFZlQwb1d1SjBhM1M0Z0NmYVZRbU5FRy1mcVRDR0lBQmR3THR3aWtvOGpKTUtIUW9lU2JmWU1WWjNnWktkbzdxSXNJNnNnXy1QR3VIb3RwOUJJUldjTld2YUJNNmItcFdKWE0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipAFBVV95cUxPeFY1WF9FUm1jTC1FaEJCcXhma3k5SndZX0JzSDcwSW03bmJFb24tLVRYaFlLY24xbk4yWm9jMkRhNkpHYXpxZzlPODNVV0R5SjZib2dQMmlTVzRVbVpqSWZKdHNrTzN5Yk1aZDY1ancxNm5Mc2lUdThLTlkzWmh5US01OEh5OUJucXhPMWRtN3Y4WXBISXlQTVVsNUdaajNHVFhhUg?oc=5</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4310,21 +4310,21 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>it</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>IT:it</t>
+          <t>FR:en</t>
         </is>
       </c>
       <c r="K71" s="1" t="n">
-        <v>46128.60453703703</v>
+        <v>46128.73241898148</v>
       </c>
     </row>
     <row r="72">
@@ -4340,22 +4340,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Caro gasolio, verso lo sciopero degli autotrasportatori. A Milano assemblea delle aziende di settore - milanopavia.news</t>
+          <t>Sciopero trasporti in arrivo: bus fermi a Milano, Monza Brianza, Lodi e Pavia. Le fasce orarie - MilanoToday</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Dear diesel, towards the hauliers' strike. Assembly of sector companies in Milan - milanopavia.news</t>
+          <t>Transport strike coming: buses stopped in Milan, Monza Brianza, Lodi and Pavia. The time slots - MilanoToday</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 17:05:26 GMT</t>
+          <t>Fri, 17 Apr 2026 10:51:18 GMT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPZmdKdGlOX0c3NGo3ajhRdEJGRzdQdk9SRkI5OTZmZzlwTXBvaGVVUWVpM1d5ZnY4QTZvWXRuZ3dMamUyb29HcWRnejN3MG1pbHE1QUhERUU5UDNNYWU0YWt6ZHF6eWlzSGwzdjRjYTdKaVJMNUgyZjJoV2xoWjZheXFSYXJ6bXdRM1FjZjBKcGNiNjN5Z1YxeTVQa1lmeHNFZTBrSFpuMEVrVHpWNUtpdVVzYWpoN1VnLS1ud0pXWk93bTFSWE1nMERxY3g3WG1heXc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihAFBVV95cUxNV3lkYTNnLU5YRjRhc2F2NjRocy10SkZISHVrc0hnQ3JfLUJYeVVHT1M4bFBBZnIwVFdONUl1eHk5aVEtTUNUeU1rTE41dEdWcTFmd0RvSmJHcWQtWk1iSDVaYkc1aHBPQ3ZxRUVHSEJZQ1VxOEtHNkhpWlhUT2VJMVo3R24?oc=5</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4379,7 +4379,7 @@
         </is>
       </c>
       <c r="K72" s="1" t="n">
-        <v>46128.71210648148</v>
+        <v>46129.45229166667</v>
       </c>
     </row>
     <row r="73">
@@ -4395,22 +4395,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Salvini sfida il 25 aprile. Milano prepara la risposta - il manifesto</t>
+          <t>Lega in corteo sabato a Milano, Conte: «Sarò in piazza per lavoro e sicurezza» - TrevisoToday</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Salvini challenges on April 25th. Milan prepares the response - the manifesto</t>
+          <t>Lega in procession on Saturday in Milan, Conte: «I will be in the square for work and safety» - TrevisoToday</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 22:09:51 GMT</t>
+          <t>Fri, 17 Apr 2026 04:02:00 GMT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQZ0dMWFkxTFE5Wm9JdURMWWFyXzBJMHRCVlJYanZTeXpsOFVGY29LTjJEUUxiQ2xQbDlSblZVR0VsQjVhYmxtZmFCd3dZMkw4bW5GaVdtWExfc1MyZFR2QlVuNURLdXY1dFVJdUlzUnFOd1pQM0Z1TVRkM3AwUHdHQk1R?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNSy1XanY2eHlnYUxHVGc5cHNSS3B5WThyZ3NHdXdCUzNRTE1Oa0l2eWcxam51ejVGTlAxSW0xQzBza1dJY1d6YWhTVXRUenV2ck13aFVoam1IZ3pTLVlwRXBhUDNOS2lxNE1EYWZGQk9rNUhUemNjUWhiaG9nc3I1VnRWVFVKSXZGTVI1aXAweHFZaVVsZHk1Sm4tMWdrMXpP?oc=5</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4434,7 +4434,7 @@
         </is>
       </c>
       <c r="K73" s="1" t="n">
-        <v>46128.92350694445</v>
+        <v>46129.16805555556</v>
       </c>
     </row>
     <row r="74">
@@ -4450,22 +4450,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>La Lega in piazza Duomo. Cassani: «Basta casi come l’egiziano di Cassano» - malpensa24</t>
+          <t>Sciopero giornalisti, il presidio a Milano: urgente rinnovo contratto - Quotidiano Nazionale</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>The League in Piazza Duomo. Cassani: «Enough of cases like Cassano's Egyptian case» - malpensa24</t>
+          <t>Journalists' strike, the garrison in Milan: urgent contract renewal - Quotidiano Nazionale</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 03:44:00 GMT</t>
+          <t>Fri, 17 Apr 2026 09:23:40 GMT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE5KWDhwQlhWWF9aQjNRNUhLSnV3Q21hZktJZnJsaVAxc0pMNXd5X2dGcTVjWFUwTGl0bFZqbGpjSVdvRXRNLXhQNWRpOGlVNTdVSmd1cGZpdWxWRVEyWjdreFJqdXFCNG85TVVVYXNn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPQTloMWdDOXRoVGVobjRmOWNWc0xzY2ZTaXR1bEd3ZEdfTE9LeVVBT00zRFQzNHlpQVNjNVI4dlU4NlBjWkdJSGlmcmhlSmVUdEs4NndmWlZZWmcycUh6Tm9pNkNMeHBzZF9vdkl0Rk5lMlRXX2hXVUpkTDg4dEh6QlcxcDV0WGlXbEVJVkRlUUc2bDJlQV9VZWpmbS04bkRuYWVkaFdRSUNlanZyNTFzOWtKMlVCQk1M?oc=5</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4489,7 +4489,7 @@
         </is>
       </c>
       <c r="K74" s="1" t="n">
-        <v>46129.15555555555</v>
+        <v>46129.39143518519</v>
       </c>
     </row>
     <row r="75">
@@ -4505,22 +4505,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Milano. Appello all’equipaggio di terra e di mare: per un 25 Aprile senza sionisti e guerrafondai - carc.it</t>
+          <t>Tre cortei e massima allerta: attesi in diecimila in Duomo - il Giornale</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Milan. Appeal to land and sea crews: for an April 25th without Zionists and warmongers - carc.it</t>
+          <t>Three marches and maximum alert: ten thousand expected in the Cathedral - il Giornale</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 15:15:31 GMT</t>
+          <t>Fri, 17 Apr 2026 05:03:45 GMT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxOTWFMQm1NNFk5Rk1xVWN5Z1BKX3llcHQ1dHExOEJMdmRPTkQwQnhVN2E4ZGdEUEFYRlE5cDRzblg1cUNsM3hadUo3NnpzMGlkSkd1Mjg2ejI1WG02WTZWbHFmbnhzZmx2ZG91Xy1Sc0J5dFhidjlpVzEyQzAya05vYUNNZy1Zb29rbG0xUzM3LUVmdDVXamMyNVJfVFRqZmZ1U01pUGxCS1lUVjlFTXhHZEt2d2tPQkMwM3U0SU5xREF4ZFRn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxPeHV5elhOUmVaYnA4czNOTUx3UVQ5aFo2eFNZZU42d2NhQ0FpT0ZpZG1Nc3FEMzJ1UzFibTRURHJCUUZjQ2QyU2dhZWhyVTI3TTlrVXZ2SXdocV9BRUZOTGRBVGVrZFFOMmRuVE9Ma1FUQXU4LXdGWjNhSE4tcnNXSjRadHZGLXFEdDZTNXRoX1BWZEZDTVd4c0x6LVNPd3ZESGQ5RjRn?oc=5</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4544,38 +4544,38 @@
         </is>
       </c>
       <c r="K75" s="1" t="n">
-        <v>46128.63577546296</v>
+        <v>46129.2109375</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Hate Crime Europe English</t>
+          <t>High Level City Italy Italian</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>("antisemitic" OR "hate crime" OR "Islamophobic" OR "racist attack" OR "extremist attack") AND ("Germany" OR "France" OR "Belgium" OR "Italy" OR "Spain" OR "UK" OR "Ireland" OR "Netherlands") AND (attack OR vandalism OR assault OR incident)</t>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Parties urged to act over candidates' racist posts - BBC</t>
+          <t>Caro gasolio, verso lo sciopero degli autotrasportatori. A Milano assemblea delle aziende di settore - milanopavia.news</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Parties urged to act over candidates' racist posts - BBC</t>
+          <t>Dear diesel, towards the hauliers' strike. Assembly of sector companies in Milan - milanopavia.news</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 14:26:40 GMT</t>
+          <t>Thu, 16 Apr 2026 17:05:26 GMT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5idmV1N1FFd1M5b3ZfTEp1M1lpdGRITDZQaDcwWFJRMkdTNW0tb2djWW1ZT25JSWFKb05NQ3NmbmNoQWI3cXloOTdUeUY4NGdWcXdmZU80ZTk3UQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0gFBVV95cUxPZmdKdGlOX0c3NGo3ajhRdEJGRzdQdk9SRkI5OTZmZzlwTXBvaGVVUWVpM1d5ZnY4QTZvWXRuZ3dMamUyb29HcWRnejN3MG1pbHE1QUhERUU5UDNNYWU0YWt6ZHF6eWlzSGwzdjRjYTdKaVJMNUgyZjJoV2xoWjZheXFSYXJ6bXdRM1FjZjBKcGNiNjN5Z1YxeTVQa1lmeHNFZTBrSFpuMEVrVHpWNUtpdVVzYWpoN1VnLS1ud0pXWk93bTFSWE1nMERxY3g3WG1heXc?oc=5</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -4585,75 +4585,350 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K76" s="1" t="n">
-        <v>46128.60185185185</v>
+        <v>46128.71210648148</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Salvini sfida il 25 aprile. Milano prepara la risposta - Il Manifesto</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Salvini challenges on April 25th. Milan prepares the response - Il Manifesto</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Thu, 16 Apr 2026 22:09:51 GMT</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxQZ0dMWFkxTFE5Wm9JdURMWWFyXzBJMHRCVlJYanZTeXpsOFVGY29LTjJEUUxiQ2xQbDlSblZVR0VsQjVhYmxtZmFCd3dZMkw4bW5GaVdtWExfc1MyZFR2QlVuNURLdXY1dFVJdUlzUnFOd1pQM0Z1TVRkM3AwUHdHQk1R?oc=5</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K77" s="1" t="n">
+        <v>46128.92350694445</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Camion cisterna ribaltato: il traffico in A14 torna scorrevole dopo ore di blocco. Morto l’autista - Il Resto del Carlino</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Tanker truck overturned: traffic on the A14 returns to flow after hours of blockage. The driver dies - Il Resto del Carlino</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Fri, 17 Apr 2026 09:27:04 GMT</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMihwFBVV95cUxNLXRIbjh0ZC1ralZoSldiRmFVNVlueDc4cTNmc2h5TnlfNUVVcHlTYnE5SURxMzN1d2ptSzkwSkRqOTU2VTktVGxoRGdyVVB1TWZxeXN3YklmNE1sT3paNXFnNndLTC10UTNqQWozWl9XbmtxU2lwSFVIajN2ME9NUmNtb19kRjg?oc=5</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K78" s="1" t="n">
+        <v>46129.3937962963</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Comunità Ebraica assente alle celebrazioni del 25 Aprile: la data coincide con lo Shabbat. “Ma il giorno della Liberazione è casa nostra” - Il Giorno</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Jewish community absent from the celebrations of April 25th: the date coincides with Shabbat. “But Liberation Day is our home” - Il Giorno</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Fri, 17 Apr 2026 12:03:04 GMT</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMif0FVX3lxTFA4MHVLU0lNc0FCWmFUN0lVTzRZX3cweDRESldCVEtDVmJvem9lXzk5ZjMtZHRaR2NLUzVodHF3aVp1OGR3SlRHTjlnZktQdEF6WkliQ0wzN0hQRmNubmVBSEtreVJUenh5T3hCa0pEcUc4V2hBVkwwRFZRRlNZUWM?oc=5</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K79" s="1" t="n">
+        <v>46129.50212962963</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>High Level City Italy Italian</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>("Milano" OR "Bologna") AND (protesta OR manifestazione OR corteo OR sciopero OR blocco OR presidio OR "sit-in") AND -calcio AND -moda AND -"settimana della moda" AND -Serie AND -mercato</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>La Lega in piazza Duomo. Cassani: «Basta casi come l’egiziano di Cassano» - malpensa24</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>The League in Piazza Duomo. Cassani: «Enough of cases like Cassano's Egyptian case» - malpensa24</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Fri, 17 Apr 2026 03:44:00 GMT</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE5KWDhwQlhWWF9aQjNRNUhLSnV3Q21hZktJZnJsaVAxc0pMNXd5X2dGcTVjWFUwTGl0bFZqbGpjSVdvRXRNLXhQNWRpOGlVNTdVSmd1cGZpdWxWRVEyWjdreFJqdXFCNG85TVVVYXNn?oc=5</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>it</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>IT:it</t>
+        </is>
+      </c>
+      <c r="K80" s="1" t="n">
+        <v>46129.15555555555</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
           <t>Hate Crime Europe English</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>("antisemitic" OR "hate crime" OR "Islamophobic" OR "racist attack" OR "extremist attack") AND ("Germany" OR "France" OR "Belgium" OR "Italy" OR "Spain" OR "UK" OR "Ireland" OR "Netherlands") AND (attack OR vandalism OR assault OR incident)</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Parties urged to act over candidates' racist posts - BBC</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Parties urged to act over candidates' racist posts - BBC</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Thu, 16 Apr 2026 14:26:40 GMT</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5idmV1N1FFd1M5b3ZfTEp1M1lpdGRITDZQaDcwWFJRMkdTNW0tb2djWW1ZT25JSWFKb05NQ3NmbmNoQWI3cXloOTdUeUY4NGdWcXdmZU80ZTk3UQ?oc=5</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>en-GB</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>GB:en</t>
+        </is>
+      </c>
+      <c r="K81" s="1" t="n">
+        <v>46128.60185185185</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Hate Crime Europe English</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>("antisemitic" OR "hate crime" OR "Islamophobic" OR "racist attack" OR "extremist attack") AND ("Germany" OR "France" OR "Belgium" OR "Italy" OR "Spain" OR "UK" OR "Ireland" OR "Netherlands") AND (attack OR vandalism OR assault OR incident)</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
         <is>
           <t>Netherlands Reports 867 Antisemitic Incidents in 2025 as Cases Remain at Alarmingly High Levels - Algemeiner.com</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D82" t="inlineStr">
         <is>
           <t>Netherlands Reports 867 Antisemitic Incidents in 2025 as Cases Remain at Alarmingly High Levels - Algemeiner.com</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E82" t="inlineStr">
         <is>
           <t>Thu, 16 Apr 2026 20:44:00 GMT</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxObXVaVGhEcThLSkRwQUJfTzdvU2dDaGtER0dad0k3alUyOTVRcXNlWWRZbzJZRnY2NW10ZWhsNjlmVDdpbXNTWGhnT1lISHpVVkg5OGRWODdoTjNnUnd4aWJvQ2g1cDh2N3IxWndnX1RWSk00NnFibnNIcUhYcExERXpNREJ6UG8tM0VtQm51dU1DbTV4WmZJNEdzZFFxWXdmNm9QdzIzU01YWE1NbFhxOG5aaC1vUk5lVWdUSHh4MGhyQU0?oc=5</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>google_rss</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
         <is>
           <t>en-GB</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="I82" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>GB:en</t>
         </is>
       </c>
-      <c r="K77" s="1" t="n">
+      <c r="K82" s="1" t="n">
         <v>46128.86388888889</v>
       </c>
     </row>
